--- a/FedEx final.xlsx
+++ b/FedEx final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0348b6f087e2cee/Desktop/fedex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1737" documentId="8_{50E72C15-D6F8-4C35-B2C2-B83030B66BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37873327-1242-4EAF-89DD-7AB6D0E467FF}"/>
+  <xr:revisionPtr revIDLastSave="1624" documentId="8_{50E72C15-D6F8-4C35-B2C2-B83030B66BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7227D94-A806-4E56-B53E-12DB630D741B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{A4D24B3A-544A-42A1-AB76-435817398B9A}"/>
+    <workbookView xWindow="28680" yWindow="-3825" windowWidth="29040" windowHeight="15720" xr2:uid="{A4D24B3A-544A-42A1-AB76-435817398B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="9" r:id="rId1"/>
@@ -26,9 +26,6 @@
     <sheet name="Comps" sheetId="6" r:id="rId11"/>
     <sheet name="Comps NF" sheetId="5" r:id="rId12"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId13"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_bdm.2DE24AA35119447C880A48293620DA86.edm" localSheetId="10" hidden="1">#REF!</definedName>
     <definedName name="_bdm.2DE24AA35119447C880A48293620DA86.edm" hidden="1">#REF!</definedName>
@@ -5175,8 +5172,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="21" fillId="15" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5201,6 +5196,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="21" fillId="15" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="8" builtinId="3"/>
@@ -5289,277 +5286,277 @@
   <volType type="realTimeData">
     <main first="refinitivshim.rtdserver.rdp.data">
       <tp>
-        <v>7210199451.6468296</v>
+        <v>1.2317889516</v>
         <stp/>
-        <stp>566</stp>
-        <stp>1038906968</stp>
+        <stp>31</stp>
+        <stp>339263609</stp>
+        <tr r="H41" s="6"/>
+      </tp>
+      <tp>
+        <v>103373082821.09</v>
+        <stp/>
+        <stp>21</stp>
+        <stp>339263609</stp>
+        <tr r="F17" s="6"/>
+      </tp>
+      <tp>
+        <v>1.1003062724155599</v>
+        <stp/>
+        <stp>11</stp>
+        <stp>339263609</stp>
+        <tr r="K8" s="6"/>
+      </tp>
+      <tp>
+        <v>14.4</v>
+        <stp/>
+        <stp>30</stp>
+        <stp>339263609</stp>
+        <tr r="G41" s="6"/>
+      </tp>
+      <tp>
+        <v>6940472605.5994997</v>
+        <stp/>
+        <stp>20</stp>
+        <stp>339263609</stp>
         <tr r="L17" s="6"/>
       </tp>
       <tp>
-        <v>3.61444149720012</v>
+        <v>50.583110861317998</v>
         <stp/>
-        <stp>567</stp>
-        <stp>1038906968</stp>
-        <tr r="H17" s="6"/>
+        <stp>10</stp>
+        <stp>339263609</stp>
+        <tr r="L8" s="6"/>
       </tp>
       <tp>
-        <v>3.9362805776598901</v>
+        <v>51.418289999999999</v>
         <stp/>
-        <stp>564</stp>
-        <stp>1038906968</stp>
-        <tr r="I17" s="6"/>
+        <stp>33</stp>
+        <stp>339263609</stp>
+        <tr r="C41" s="6"/>
       </tp>
       <tp>
-        <v>100829895219.57001</v>
+        <v>13111967026.9769</v>
         <stp/>
-        <stp>565</stp>
-        <stp>1038906968</stp>
-        <tr r="E17" s="6"/>
+        <stp>23</stp>
+        <stp>339263609</stp>
+        <tr r="P17" s="6"/>
       </tp>
       <tp>
-        <v>104825744332.44901</v>
+        <v>12534163102.224501</v>
         <stp/>
-        <stp>562</stp>
-        <stp>1038906968</stp>
-        <tr r="F17" s="6"/>
+        <stp>13</stp>
+        <stp>339263609</stp>
+        <tr r="O17" s="6"/>
       </tp>
       <tp>
-        <v>4.3358679634541701</v>
+        <v>38.799859390800002</v>
         <stp/>
-        <stp>563</stp>
-        <stp>1038906968</stp>
+        <stp>32</stp>
+        <stp>339263609</stp>
+        <tr r="L41" s="6"/>
+      </tp>
+      <tp>
+        <v>4.2056087773422099</v>
+        <stp/>
+        <stp>22</stp>
+        <stp>339263609</stp>
         <tr r="J17" s="6"/>
       </tp>
       <tp>
-        <v>98861856305.470505</v>
+        <v>7387939876.1337004</v>
         <stp/>
-        <stp>560</stp>
-        <stp>1038906968</stp>
-        <tr r="D17" s="6"/>
+        <stp>12</stp>
+        <stp>339263609</stp>
+        <tr r="M17" s="6"/>
       </tp>
       <tp>
-        <v>13361105063.365801</v>
+        <v>84186000000</v>
         <stp/>
-        <stp>561</stp>
-        <stp>1038906968</stp>
-        <tr r="P17" s="6"/>
+        <stp>35</stp>
+        <stp>339263609</stp>
+        <tr r="J41" s="6"/>
+      </tp>
+      <tp>
+        <v>4.8789999999999996</v>
+        <stp/>
+        <stp>25</stp>
+        <stp>339263609</stp>
+        <tr r="F41" s="6"/>
+      </tp>
+      <tp>
+        <v>6334257953.4007101</v>
+        <stp/>
+        <stp>15</stp>
+        <stp>339263609</stp>
+        <tr r="K17" s="6"/>
+      </tp>
+      <tp>
+        <v>37.062981422699998</v>
+        <stp/>
+        <stp>34</stp>
+        <stp>339263609</stp>
+        <tr r="I41" s="6"/>
+      </tp>
+      <tp>
+        <v>11462678007.777399</v>
+        <stp/>
+        <stp>24</stp>
+        <stp>339263609</stp>
+        <tr r="N17" s="6"/>
       </tp>
       <tp>
         <v>3.0532176475048498</v>
         <stp/>
-        <stp>568</stp>
-        <stp>1038906968</stp>
+        <stp>14</stp>
+        <stp>339263609</stp>
         <tr r="G17" s="6"/>
       </tp>
       <tp>
-        <v>12871744921.898001</v>
+        <v>0.95162999999999998</v>
         <stp/>
-        <stp>569</stp>
-        <stp>1038906968</stp>
-        <tr r="O17" s="6"/>
+        <stp>37</stp>
+        <stp>339263609</stp>
+        <tr r="N41" s="6"/>
       </tp>
       <tp>
         <v>0.89749999999999996</v>
         <stp/>
-        <stp>576</stp>
-        <stp>1038906968</stp>
+        <stp>27</stp>
+        <stp>339263609</stp>
         <tr r="M41" s="6"/>
       </tp>
       <tp>
-        <v>1.2317889516</v>
+        <v>99609137435.921204</v>
         <stp/>
-        <stp>577</stp>
-        <stp>1038906968</stp>
-        <tr r="H41" s="6"/>
+        <stp>17</stp>
+        <stp>339263609</stp>
+        <tr r="E17" s="6"/>
       </tp>
       <tp>
-        <v>38.799859390800002</v>
+        <v>12908000000</v>
         <stp/>
-        <stp>574</stp>
-        <stp>1038906968</stp>
-        <tr r="L41" s="6"/>
+        <stp>36</stp>
+        <stp>339263609</stp>
+        <tr r="J41" s="6"/>
       </tp>
       <tp>
         <v>6.9916600000000004</v>
         <stp/>
-        <stp>575</stp>
-        <stp>1038906968</stp>
+        <stp>26</stp>
+        <stp>339263609</stp>
         <tr r="D41" s="6"/>
       </tp>
       <tp>
-        <v>4.8789999999999996</v>
+        <v>97142373176.219498</v>
         <stp/>
-        <stp>572</stp>
-        <stp>1038906968</stp>
-        <tr r="F41" s="6"/>
+        <stp>16</stp>
+        <stp>339263609</stp>
+        <tr r="D17" s="6"/>
       </tp>
       <tp>
         <v>3.9579</v>
         <stp/>
-        <stp>573</stp>
-        <stp>1038906968</stp>
+        <stp>39</stp>
+        <stp>339263609</stp>
         <tr r="E41" s="6"/>
       </tp>
       <tp>
-        <v>6334257953.4007101</v>
+        <v>928000000</v>
         <stp/>
-        <stp>570</stp>
-        <stp>1038906968</stp>
-        <tr r="K17" s="6"/>
+        <stp>29</stp>
+        <stp>339263609</stp>
+        <tr r="O41" s="6"/>
       </tp>
       <tp>
-        <v>51.418289999999999</v>
+        <v>3.8056296536846701</v>
         <stp/>
-        <stp>571</stp>
-        <stp>1038906968</stp>
-        <tr r="C41" s="6"/>
+        <stp>19</stp>
+        <stp>339263609</stp>
+        <tr r="I17" s="6"/>
       </tp>
       <tp>
-        <v>37.062981422699998</v>
+        <v>101.5046442231</v>
         <stp/>
-        <stp>578</stp>
-        <stp>1038906968</stp>
-        <tr r="I41" s="6"/>
+        <stp>38</stp>
+        <stp>339263609</stp>
+        <tr r="K41" s="6"/>
       </tp>
       <tp>
-        <v>0.95162999999999998</v>
+        <v>10502000000</v>
         <stp/>
-        <stp>579</stp>
-        <stp>1038906968</stp>
-        <tr r="N41" s="6"/>
+        <stp>28</stp>
+        <stp>339263609</stp>
+        <tr r="O41" s="6"/>
       </tp>
       <tp>
-        <v>58.725526107454698</v>
+        <v>3.4536545197281399</v>
         <stp/>
-        <stp>547</stp>
-        <stp>1038906968</stp>
+        <stp>18</stp>
+        <stp>339263609</stp>
+        <tr r="H17" s="6"/>
+      </tp>
+      <tp>
+        <v>46.9028507520067</v>
+        <stp/>
+        <stp>4</stp>
+        <stp>339263609</stp>
         <tr r="C8" s="6"/>
       </tp>
+      <tp t="s">
+        <v>Deutsche Post AG</v>
+        <stp/>
+        <stp>5</stp>
+        <stp>339263609</stp>
+        <tr r="A8" s="6"/>
+      </tp>
       <tp>
-        <v>52.601676930035097</v>
+        <v>7.3</v>
         <stp/>
-        <stp>548</stp>
-        <stp>1038906968</stp>
-        <tr r="L8" s="6"/>
+        <stp>6</stp>
+        <stp>339263609</stp>
+        <tr r="Q17" s="6"/>
+      </tp>
+      <tp>
+        <v>1200000000</v>
+        <stp/>
+        <stp>7</stp>
+        <stp>339263609</stp>
+        <tr r="E8" s="6"/>
+      </tp>
+      <tp>
+        <v>24632984781.033199</v>
+        <stp/>
+        <stp>1</stp>
+        <stp>339263609</stp>
+        <tr r="J8" s="6"/>
+      </tp>
+      <tp>
+        <v>1472202091.3138001</v>
+        <stp/>
+        <stp>2</stp>
+        <stp>339263609</stp>
+        <tr r="H8" s="6"/>
       </tp>
       <tp>
         <v>25003623563.5159</v>
         <stp/>
-        <stp>549</stp>
-        <stp>1038906968</stp>
+        <stp>3</stp>
+        <stp>339263609</stp>
         <tr r="G8" s="6"/>
       </tp>
       <tp>
-        <v>24632984781.033199</v>
+        <v>49.431525756795999</v>
         <stp/>
-        <stp>556</stp>
-        <stp>1038906968</stp>
-        <tr r="J8" s="6"/>
-      </tp>
-      <tp>
-        <v>9.9</v>
-        <stp/>
-        <stp>557</stp>
-        <stp>1038906968</stp>
-        <tr r="Q17" s="6"/>
+        <stp>8</stp>
+        <stp>339263609</stp>
+        <tr r="D8" s="6"/>
       </tp>
       <tp>
         <v>87158090899.679001</v>
         <stp/>
-        <stp>554</stp>
-        <stp>1038906968</stp>
+        <stp>9</stp>
+        <stp>339263609</stp>
         <tr r="C17" s="6"/>
-      </tp>
-      <tp>
-        <v>1.2140823476417</v>
-        <stp/>
-        <stp>555</stp>
-        <stp>1038906968</stp>
-        <tr r="K8" s="6"/>
-      </tp>
-      <tp>
-        <v>58.831870118514502</v>
-        <stp/>
-        <stp>552</stp>
-        <stp>1038906968</stp>
-        <tr r="D8" s="6"/>
-      </tp>
-      <tp t="s">
-        <v>Deutsche Post AG</v>
-        <stp/>
-        <stp>553</stp>
-        <stp>1038906968</stp>
-        <tr r="A8" s="6"/>
-      </tp>
-      <tp>
-        <v>1472202091.3138001</v>
-        <stp/>
-        <stp>550</stp>
-        <stp>1038906968</stp>
-        <tr r="H8" s="6"/>
-      </tp>
-      <tp>
-        <v>1150000000</v>
-        <stp/>
-        <stp>551</stp>
-        <stp>1038906968</stp>
-        <tr r="E8" s="6"/>
-      </tp>
-      <tp>
-        <v>7546310474.50634</v>
-        <stp/>
-        <stp>558</stp>
-        <stp>1038906968</stp>
-        <tr r="M17" s="6"/>
-      </tp>
-      <tp>
-        <v>11462678007.777399</v>
-        <stp/>
-        <stp>559</stp>
-        <stp>1038906968</stp>
-        <tr r="N17" s="6"/>
-      </tp>
-      <tp>
-        <v>84186000000</v>
-        <stp/>
-        <stp>584</stp>
-        <stp>1038906968</stp>
-        <tr r="J41" s="6"/>
-      </tp>
-      <tp>
-        <v>12908000000</v>
-        <stp/>
-        <stp>585</stp>
-        <stp>1038906968</stp>
-        <tr r="J41" s="6"/>
-      </tp>
-      <tp>
-        <v>101.5046442231</v>
-        <stp/>
-        <stp>582</stp>
-        <stp>1038906968</stp>
-        <tr r="K41" s="6"/>
-      </tp>
-      <tp>
-        <v>14.4</v>
-        <stp/>
-        <stp>583</stp>
-        <stp>1038906968</stp>
-        <tr r="G41" s="6"/>
-      </tp>
-      <tp>
-        <v>10502000000</v>
-        <stp/>
-        <stp>580</stp>
-        <stp>1038906968</stp>
-        <tr r="O41" s="6"/>
-      </tp>
-      <tp>
-        <v>928000000</v>
-        <stp/>
-        <stp>581</stp>
-        <stp>1038906968</stp>
-        <tr r="O41" s="6"/>
       </tp>
     </main>
   </volType>
@@ -5669,44 +5666,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cover"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Ke"/>
-      <sheetName val="Revenue"/>
-      <sheetName val="Cost of sales"/>
-      <sheetName val="Income statement"/>
-      <sheetName val="Balance sheet"/>
-      <sheetName val="Cash flow"/>
-      <sheetName val="Changes in Equity"/>
-      <sheetName val="Schedules"/>
-      <sheetName val="Comps"/>
-      <sheetName val="Comps no formula"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6229,7 +6188,7 @@
       </c>
       <c r="E11" s="205">
         <f ca="1">TODAY()</f>
-        <v>46061</v>
+        <v>45959</v>
       </c>
       <c r="F11" s="199"/>
       <c r="G11" s="199"/>
@@ -6296,9 +6255,9 @@
       <c r="D15" s="204" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="207" t="e">
+      <c r="E15" s="207" t="str">
         <f ca="1">IF(E23&gt;=Ke!D38,"BUY","SELL")</f>
-        <v>#VALUE!</v>
+        <v>BUY</v>
       </c>
       <c r="F15" s="199"/>
       <c r="G15" s="199"/>
@@ -6328,7 +6287,8 @@
         <v>15</v>
       </c>
       <c r="E17" s="209">
-        <v>249</v>
+        <f>Ke!D15</f>
+        <v>249.31</v>
       </c>
       <c r="F17" s="199"/>
       <c r="G17" s="199"/>
@@ -6344,9 +6304,9 @@
       <c r="D18" s="210" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="211" t="e">
+      <c r="E18" s="211">
         <f ca="1">DCF!B8</f>
-        <v>#VALUE!</v>
+        <v>272.05149552257603</v>
       </c>
       <c r="F18" s="199"/>
       <c r="G18" s="199"/>
@@ -6362,9 +6322,9 @@
       <c r="D19" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="211" t="e">
+      <c r="E19" s="211">
         <f ca="1">DCF!B9</f>
-        <v>#VALUE!</v>
+        <v>289.87884277369778</v>
       </c>
       <c r="F19" s="199"/>
       <c r="G19" s="199"/>
@@ -6380,9 +6340,9 @@
       <c r="D20" s="214" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="215" t="e">
+      <c r="E20" s="215">
         <f ca="1">E18/E17-1</f>
-        <v>#VALUE!</v>
+        <v>9.1217743061152934E-2</v>
       </c>
       <c r="F20" s="199"/>
       <c r="G20" s="199"/>
@@ -6398,9 +6358,9 @@
       <c r="D21" s="214" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="215" t="e">
+      <c r="E21" s="215">
         <f ca="1">E19/E17-1</f>
-        <v>#VALUE!</v>
+        <v>0.162724490689093</v>
       </c>
       <c r="F21" s="199"/>
       <c r="G21" s="199"/>
@@ -6409,10 +6369,10 @@
     </row>
     <row r="22" spans="3:9" ht="18">
       <c r="C22" s="199"/>
-      <c r="D22" s="460" t="s">
+      <c r="D22" s="468" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="461">
+      <c r="E22" s="469">
         <v>2.3900000000000001E-2</v>
       </c>
       <c r="F22" s="199"/>
@@ -6424,9 +6384,9 @@
       <c r="D23" s="216" t="s">
         <v>542</v>
       </c>
-      <c r="E23" s="217" t="e">
+      <c r="E23" s="217">
         <f ca="1">E21+E22</f>
-        <v>#VALUE!</v>
+        <v>0.18662449068909301</v>
       </c>
     </row>
   </sheetData>
@@ -6482,25 +6442,25 @@
         <f>'Income statement'!F27</f>
         <v>4092</v>
       </c>
-      <c r="C2" s="191" t="e">
+      <c r="C2" s="191">
         <f>'Income statement'!H27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D2" s="191" t="e">
+        <v>4912.214417088323</v>
+      </c>
+      <c r="D2" s="191">
         <f>'Income statement'!I27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E2" s="191" t="e">
+        <v>5798.957783050444</v>
+      </c>
+      <c r="E2" s="191">
         <f>'Income statement'!J27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F2" s="191" t="e">
+        <v>5787.2821787065695</v>
+      </c>
+      <c r="F2" s="191">
         <f>'Income statement'!K27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G2" s="191" t="e">
+        <v>5883.6479534875252</v>
+      </c>
+      <c r="G2" s="191">
         <f>'Income statement'!L27</f>
-        <v>#VALUE!</v>
+        <v>5814.1306532332665</v>
       </c>
       <c r="J2" s="158"/>
     </row>
@@ -6558,25 +6518,25 @@
         <f>'Balance sheet'!E7-'Balance sheet'!F7</f>
         <v>-1281</v>
       </c>
-      <c r="C7" s="191" t="e">
+      <c r="C7" s="191">
         <f>'Balance sheet'!F7-'Balance sheet'!G7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D7" s="191" t="e">
+        <v>160.52565926163152</v>
+      </c>
+      <c r="D7" s="191">
         <f>'Balance sheet'!G7-'Balance sheet'!H7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E7" s="191" t="e">
+        <v>-206.46319403946109</v>
+      </c>
+      <c r="E7" s="191">
         <f>'Balance sheet'!H7-'Balance sheet'!I7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F7" s="191" t="e">
+        <v>-252.96518999071668</v>
+      </c>
+      <c r="F7" s="191">
         <f>'Balance sheet'!I7-'Balance sheet'!J7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G7" s="191" t="e">
+        <v>-244.87790236293949</v>
+      </c>
+      <c r="G7" s="191">
         <f>'Balance sheet'!J7-'Balance sheet'!K7</f>
-        <v>#VALUE!</v>
+        <v>-251.33568372680384</v>
       </c>
       <c r="J7" s="158"/>
     </row>
@@ -6588,25 +6548,25 @@
         <f>'Balance sheet'!E8-'Balance sheet'!F8</f>
         <v>12</v>
       </c>
-      <c r="C8" s="191" t="e">
+      <c r="C8" s="191">
         <f>'Balance sheet'!F8-'Balance sheet'!G8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="191" t="e">
+        <v>8.2658981436788963</v>
+      </c>
+      <c r="D8" s="191">
         <f>'Balance sheet'!G8-'Balance sheet'!H8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="191" t="e">
+        <v>5.7382066863992804</v>
+      </c>
+      <c r="E8" s="191">
         <f>'Balance sheet'!H8-'Balance sheet'!I8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F8" s="191" t="e">
+        <v>-13.042870659463347</v>
+      </c>
+      <c r="F8" s="191">
         <f>'Balance sheet'!I8-'Balance sheet'!J8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G8" s="191" t="e">
+        <v>4.211872008308319</v>
+      </c>
+      <c r="G8" s="191">
         <f>'Balance sheet'!J8-'Balance sheet'!K8</f>
-        <v>#VALUE!</v>
+        <v>-12.580438253268994</v>
       </c>
       <c r="J8" s="158"/>
     </row>
@@ -6618,25 +6578,25 @@
         <f>'Balance sheet'!E9-'Balance sheet'!F9</f>
         <v>91</v>
       </c>
-      <c r="C9" s="191" t="e">
+      <c r="C9" s="191">
         <f>'Balance sheet'!F9-'Balance sheet'!G9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D9" s="191" t="e">
+        <v>-19.015127341684661</v>
+      </c>
+      <c r="D9" s="191">
         <f>'Balance sheet'!G9-'Balance sheet'!H9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E9" s="191" t="e">
+        <v>-3.9726235179125524</v>
+      </c>
+      <c r="E9" s="191">
         <f>'Balance sheet'!H9-'Balance sheet'!I9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F9" s="191" t="e">
+        <v>-21.721652686762354</v>
+      </c>
+      <c r="F9" s="191">
         <f>'Balance sheet'!I9-'Balance sheet'!J9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G9" s="191" t="e">
+        <v>-20.166878161439627</v>
+      </c>
+      <c r="G9" s="191">
         <f>'Balance sheet'!J9-'Balance sheet'!K9</f>
-        <v>#VALUE!</v>
+        <v>-23.167593319340767</v>
       </c>
       <c r="J9" s="158"/>
     </row>
@@ -6876,25 +6836,25 @@
         <f>'Balance sheet'!E23-'Balance sheet'!F23</f>
         <v>-772</v>
       </c>
-      <c r="C23" s="191" t="e">
+      <c r="C23" s="191">
         <f>'Balance sheet'!F23-'Balance sheet'!G23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D23" s="191" t="e">
+        <v>349.5153229540465</v>
+      </c>
+      <c r="D23" s="191">
         <f>'Balance sheet'!G23-'Balance sheet'!H23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E23" s="191" t="e">
+        <v>-77.252038617774815</v>
+      </c>
+      <c r="E23" s="191">
         <f>'Balance sheet'!H23-'Balance sheet'!I23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F23" s="191" t="e">
+        <v>-94.651624068068486</v>
+      </c>
+      <c r="F23" s="191">
         <f>'Balance sheet'!I23-'Balance sheet'!J23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G23" s="191" t="e">
+        <v>-91.625615199801359</v>
+      </c>
+      <c r="G23" s="191">
         <f>'Balance sheet'!J23-'Balance sheet'!K23</f>
-        <v>#VALUE!</v>
+        <v>-94.041914035182344</v>
       </c>
       <c r="J23" s="158"/>
     </row>
@@ -6985,25 +6945,25 @@
         <f>'Balance sheet'!F29-'Balance sheet'!E29</f>
         <v>58</v>
       </c>
-      <c r="C29" s="191" t="e">
+      <c r="C29" s="191">
         <f>'Balance sheet'!G29-'Balance sheet'!F29</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D29" s="191" t="e">
+        <v>-92.600487230810359</v>
+      </c>
+      <c r="D29" s="191">
         <f>'Balance sheet'!H29-'Balance sheet'!G29</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E29" s="191" t="e">
+        <v>-17.563959055983105</v>
+      </c>
+      <c r="E29" s="191">
         <f>'Balance sheet'!I29-'Balance sheet'!H29</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F29" s="191" t="e">
+        <v>59.569706472242615</v>
+      </c>
+      <c r="F29" s="191">
         <f>'Balance sheet'!J29-'Balance sheet'!I29</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G29" s="191" t="e">
+        <v>57.884568464086897</v>
+      </c>
+      <c r="G29" s="191">
         <f>'Balance sheet'!K29-'Balance sheet'!J29</f>
-        <v>#VALUE!</v>
+        <v>59.430773884579139</v>
       </c>
       <c r="J29" s="158"/>
     </row>
@@ -7015,25 +6975,25 @@
         <f>'Balance sheet'!F30-'Balance sheet'!E30</f>
         <v>503</v>
       </c>
-      <c r="C30" s="191" t="e">
+      <c r="C30" s="191">
         <f>'Balance sheet'!G30-'Balance sheet'!F30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D30" s="191" t="e">
+        <v>31.360866955069014</v>
+      </c>
+      <c r="D30" s="191">
         <f>'Balance sheet'!H30-'Balance sheet'!G30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E30" s="191" t="e">
+        <v>15.853452438529985</v>
+      </c>
+      <c r="E30" s="191">
         <f>'Balance sheet'!I30-'Balance sheet'!H30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F30" s="191" t="e">
+        <v>86.684073183158944</v>
+      </c>
+      <c r="F30" s="191">
         <f>'Balance sheet'!J30-'Balance sheet'!I30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G30" s="191" t="e">
+        <v>80.47947214842543</v>
+      </c>
+      <c r="G30" s="191">
         <f>'Balance sheet'!K30-'Balance sheet'!J30</f>
-        <v>#VALUE!</v>
+        <v>92.454353438551607</v>
       </c>
       <c r="J30" s="158"/>
     </row>
@@ -7075,25 +7035,25 @@
         <f>'Balance sheet'!F32-'Balance sheet'!E32</f>
         <v>33</v>
       </c>
-      <c r="C32" s="191" t="e">
+      <c r="C32" s="191">
         <f>'Balance sheet'!G32-'Balance sheet'!F32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" s="191" t="e">
+        <v>-123.94510199675551</v>
+      </c>
+      <c r="D32" s="191">
         <f>'Balance sheet'!H32-'Balance sheet'!G32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E32" s="191" t="e">
+        <v>20.740143088552031</v>
+      </c>
+      <c r="E32" s="191">
         <f>'Balance sheet'!I32-'Balance sheet'!H32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F32" s="191" t="e">
+        <v>113.40369476542401</v>
+      </c>
+      <c r="F32" s="191">
         <f>'Balance sheet'!J32-'Balance sheet'!I32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G32" s="191" t="e">
+        <v>105.28657871346604</v>
+      </c>
+      <c r="G32" s="191">
         <f>'Balance sheet'!K32-'Balance sheet'!J32</f>
-        <v>#VALUE!</v>
+        <v>120.95261438542002</v>
       </c>
       <c r="J32" s="158"/>
     </row>
@@ -7237,25 +7197,25 @@
         <f>'Balance sheet'!F38-'Balance sheet'!E38</f>
         <v>332</v>
       </c>
-      <c r="C38" s="191" t="e">
+      <c r="C38" s="191">
         <f>'Balance sheet'!G38-'Balance sheet'!F38</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D38" s="191" t="e">
+        <v>307.7874924623311</v>
+      </c>
+      <c r="D38" s="191">
         <f>'Balance sheet'!H38-'Balance sheet'!G38</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E38" s="191" t="e">
+        <v>325.99608062030893</v>
+      </c>
+      <c r="E38" s="191">
         <f>'Balance sheet'!I38-'Balance sheet'!H38</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F38" s="191" t="e">
+        <v>422.83002572467376</v>
+      </c>
+      <c r="F38" s="191">
         <f>'Balance sheet'!J38-'Balance sheet'!I38</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G38" s="191" t="e">
+        <v>428.32357412621514</v>
+      </c>
+      <c r="G38" s="191">
         <f>'Balance sheet'!K38-'Balance sheet'!J38</f>
-        <v>#VALUE!</v>
+        <v>459.46075310307879</v>
       </c>
       <c r="J38" s="158"/>
     </row>
@@ -7297,25 +7257,25 @@
         <f>'Balance sheet'!F40-'Balance sheet'!E40</f>
         <v>94</v>
       </c>
-      <c r="C40" s="191" t="e">
+      <c r="C40" s="191">
         <f>'Balance sheet'!G40-'Balance sheet'!F40</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D40" s="191" t="e">
+        <v>-7.0943215267790265</v>
+      </c>
+      <c r="D40" s="191">
         <f>'Balance sheet'!H40-'Balance sheet'!G40</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E40" s="191" t="e">
+        <v>14.29367222092435</v>
+      </c>
+      <c r="E40" s="191">
         <f>'Balance sheet'!I40-'Balance sheet'!H40</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F40" s="191" t="e">
+        <v>17.513056144719485</v>
+      </c>
+      <c r="F40" s="191">
         <f>'Balance sheet'!J40-'Balance sheet'!I40</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G40" s="191" t="e">
+        <v>16.953164397207047</v>
+      </c>
+      <c r="G40" s="191">
         <f>'Balance sheet'!K40-'Balance sheet'!J40</f>
-        <v>#VALUE!</v>
+        <v>17.400243647912589</v>
       </c>
       <c r="J40" s="158"/>
     </row>
@@ -7592,25 +7552,25 @@
         <v>410</v>
       </c>
       <c r="B54" s="179"/>
-      <c r="C54" s="191" t="e">
+      <c r="C54" s="191">
         <f>SUM(C2:C47)+C52</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D54" s="191" t="e">
+        <v>806.21468347424752</v>
+      </c>
+      <c r="D54" s="191">
         <f t="shared" ref="D54:G54" si="1">SUM(D2:D47)+D52</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E54" s="191" t="e">
+        <v>2861.714555622124</v>
+      </c>
+      <c r="E54" s="191">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F54" s="191" t="e">
+        <v>3008.6540679883424</v>
+      </c>
+      <c r="F54" s="191">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G54" s="191" t="e">
+        <v>3023.4367549566923</v>
+      </c>
+      <c r="G54" s="191">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+        <v>2406.2721386847061</v>
       </c>
       <c r="K54" s="158"/>
     </row>
@@ -7632,21 +7592,21 @@
         <f>'Balance sheet'!F6</f>
         <v>5502</v>
       </c>
-      <c r="D56" s="191" t="e">
+      <c r="D56" s="191">
         <f>C57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E56" s="191" t="e">
+        <v>6308.2146834742471</v>
+      </c>
+      <c r="E56" s="191">
         <f t="shared" ref="E56:G56" si="2">D57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F56" s="191" t="e">
+        <v>9169.929239096371</v>
+      </c>
+      <c r="F56" s="191">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G56" s="191" t="e">
+        <v>12178.583307084713</v>
+      </c>
+      <c r="G56" s="191">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>15202.020062041405</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -7654,25 +7614,25 @@
         <v>412</v>
       </c>
       <c r="B57" s="357"/>
-      <c r="C57" s="358" t="e">
+      <c r="C57" s="358">
         <f>C56+C54</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" s="358" t="e">
+        <v>6308.2146834742471</v>
+      </c>
+      <c r="D57" s="358">
         <f>D56+D54</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E57" s="358" t="e">
+        <v>9169.929239096371</v>
+      </c>
+      <c r="E57" s="358">
         <f>E56+E54</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F57" s="358" t="e">
+        <v>12178.583307084713</v>
+      </c>
+      <c r="F57" s="358">
         <f>F56+F54</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G57" s="358" t="e">
+        <v>15202.020062041405</v>
+      </c>
+      <c r="G57" s="358">
         <f>G56+G54</f>
-        <v>#VALUE!</v>
+        <v>17608.292200726111</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -7689,47 +7649,47 @@
         <v>413</v>
       </c>
       <c r="B59" s="179"/>
-      <c r="C59" s="191" t="e">
+      <c r="C59" s="191">
         <f>C54-C52-C51</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D59" s="191" t="e">
+        <v>4634.6456263393384</v>
+      </c>
+      <c r="D59" s="191">
         <f>D54-D52-D51</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E59" s="191" t="e">
+        <v>6720.3146224073289</v>
+      </c>
+      <c r="E59" s="191">
         <f>E54-E52-E51</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F59" s="191" t="e">
+        <v>6901.7994785816281</v>
+      </c>
+      <c r="F59" s="191">
         <f>F54-F52-F51</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G59" s="191" t="e">
+        <v>6955.683681815789</v>
+      </c>
+      <c r="G59" s="191">
         <f>G54-G52-G51</f>
-        <v>#VALUE!</v>
+        <v>6382.3735703889888</v>
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="C61" s="196" t="e">
+      <c r="C61" s="196">
         <f>C59-C2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D61" s="196" t="e">
+        <v>-277.56879074898461</v>
+      </c>
+      <c r="D61" s="196">
         <f t="shared" ref="D61:G61" si="3">D59-D2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E61" s="196" t="e">
+        <v>921.35683935688485</v>
+      </c>
+      <c r="E61" s="196">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F61" s="196" t="e">
+        <v>1114.5172998750586</v>
+      </c>
+      <c r="F61" s="196">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G61" s="196" t="e">
+        <v>1072.0357283282638</v>
+      </c>
+      <c r="G61" s="196">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v>568.24291715572235</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -8033,19 +7993,19 @@
       </c>
       <c r="C8" s="134">
         <f>IF(B8="","",_xll.RDP.Data($B8,"TR.PriceClose","Curn=#1",,$C$1))</f>
-        <v>58.725526107454698</v>
+        <v>46.9028507520067</v>
       </c>
       <c r="D8" s="31">
         <f>IF($B8="","",_xll.RDP.Data($B8,"MAX(TR.PriceHigh(SDate=0D,EDate=0D-364C))/*52 Week High*/","Curn=#1",,$C$1))</f>
-        <v>58.831870118514502</v>
+        <v>49.431525756795999</v>
       </c>
       <c r="E8" s="133">
         <f>IF(B8="","",_xll.RDP.Data($B8,"TR.CompanySharesOutstanding(SDate=0)/*# Shares Outstanding*/")/1000000)</f>
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="132">
         <f>IF(B8="","",C8*E8)</f>
-        <v>67534.355023572905</v>
+        <v>56283.420902408041</v>
       </c>
       <c r="G8" s="132" cm="1">
         <f t="array" ref="G8">IF($B8="","",_xll.RDP.Data($B8,"TR.TotalDebtOutstanding","Curn=#1",,$C$1)/1000000)</f>
@@ -8057,7 +8017,7 @@
       </c>
       <c r="I8" s="132">
         <f>IF(B8="","",F8+G8-H8)</f>
-        <v>91065.776495775004</v>
+        <v>79814.842374610147</v>
       </c>
       <c r="J8" s="132" cm="1">
         <f t="array" ref="J8">IF($B8="","",_xll.RDP.Data($B8,"TR.TotalEquity","Curn=#1",,$C$1)/1000000)</f>
@@ -8065,11 +8025,11 @@
       </c>
       <c r="K8" s="131">
         <f>IF($B8="","",_xll.RDP.Data($B8,"TR.BetaFiveYear/*Beta 5 Year Monthly*//*Beta 5 Year Monthly*/"))</f>
-        <v>1.2140823476417</v>
+        <v>1.1003062724155599</v>
       </c>
       <c r="L8" s="130">
         <f>IF(B8="","",_xll.RDP.Data($B8,"TR.PriceTargetMean","Curn=#1",,$C$1))</f>
-        <v>52.601676930035097</v>
+        <v>50.583110861317998</v>
       </c>
       <c r="M8" s="122"/>
       <c r="N8" s="6"/>
@@ -8491,15 +8451,15 @@
       </c>
       <c r="D17" s="114" cm="1">
         <f t="array" ref="D17">IF($B17="","",_xll.RDP.Data($B17,"TR.RevenueMean","Period=FY1 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>98861.856305470501</v>
+        <v>97142.373176219495</v>
       </c>
       <c r="E17" s="114" cm="1">
         <f t="array" ref="E17">IF($B17="","",_xll.RDP.Data($B17,"TR.RevenueMean","Period=FY2 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>100829.89521957001</v>
+        <v>99609.137435921206</v>
       </c>
       <c r="F17" s="113" cm="1">
         <f t="array" ref="F17">IF($B17="","",_xll.RDP.Data($B17,"TR.RevenueMean","Period=FY3 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>104825.744332449</v>
+        <v>103373.08282108999</v>
       </c>
       <c r="G17" s="110">
         <f>IF($B17="","",_xll.RDP.Data($B17,"TR.EPSMean","Period=FY0 Frq=D SDate=1D Curn=#1",,$C$1))</f>
@@ -8507,15 +8467,15 @@
       </c>
       <c r="H17" s="110">
         <f>IF($B17="","",_xll.RDP.Data($B17,"TR.EPSMean","Period=FY1 Frq=D SDate=1D Curn=#1",,$C$1))</f>
-        <v>3.61444149720012</v>
+        <v>3.4536545197281399</v>
       </c>
       <c r="I17" s="110">
         <f>IF($B17="","",_xll.RDP.Data($B17,"TR.EPSMean","Period=FY2 Frq=D SDate=1D Curn=#1",,$C$1))</f>
-        <v>3.9362805776598901</v>
+        <v>3.8056296536846701</v>
       </c>
       <c r="J17" s="112">
         <f>IF($B17="","",_xll.RDP.Data($B17,"TR.EPSMean","Period=FY3 Frq=D SDate=1D Curn=#1",,$C$1))</f>
-        <v>4.3358679634541701</v>
+        <v>4.2056087773422099</v>
       </c>
       <c r="K17" s="110" cm="1">
         <f t="array" ref="K17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITMean","Period=FY0 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
@@ -8523,11 +8483,11 @@
       </c>
       <c r="L17" s="110" cm="1">
         <f t="array" ref="L17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITMean","Period=FY1 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>7210.1994516468294</v>
+        <v>6940.4726055994997</v>
       </c>
       <c r="M17" s="112" cm="1">
         <f t="array" ref="M17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITMean","Period=FY2 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>7546.3104745063401</v>
+        <v>7387.9398761337006</v>
       </c>
       <c r="N17" s="111" cm="1">
         <f t="array" ref="N17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITDAMean","Period=FY0 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
@@ -8535,15 +8495,15 @@
       </c>
       <c r="O17" s="110" cm="1">
         <f t="array" ref="O17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITDAMean","Period=FY1 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>12871.744921898</v>
+        <v>12534.1631022245</v>
       </c>
       <c r="P17" s="110" cm="1">
         <f t="array" ref="P17">IF($B17="","",_xll.RDP.Data($B17,"TR.EBITDAMean","Period=FY2 Frq=D SDate=1D Curn=#1",,$C$1)/1000000)</f>
-        <v>13361.105063365801</v>
+        <v>13111.967026976899</v>
       </c>
       <c r="Q17" s="109" cm="1">
         <f t="array" ref="Q17">IF($B17="","",_xll.RDP.Data($B17,"TR.LTGMean",,)/100)</f>
-        <v>9.9000000000000005E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="R17" s="108" t="s">
         <v>447</v>
@@ -8968,59 +8928,59 @@
       </c>
       <c r="C26" s="89">
         <f t="shared" si="0"/>
-        <v>58.725526107454698</v>
+        <v>46.9028507520067</v>
       </c>
       <c r="D26" s="88">
         <f>IF(OR(B26="",ISNUMBER(F8)=FALSE,ISNUMBER(J8)=FALSE),"",F8/J8)</f>
-        <v>2.7416228940137501</v>
+        <v>2.2848802693916701</v>
       </c>
       <c r="E26" s="88">
         <f t="shared" si="1"/>
-        <v>0.68311841945290186</v>
+        <v>0.57939104288000087</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="1"/>
-        <v>0.66978503623858976</v>
+        <v>0.56504274960332124</v>
       </c>
       <c r="G26" s="86">
         <f t="shared" si="1"/>
-        <v>0.64425352239228051</v>
+        <v>0.54446882463415514</v>
       </c>
       <c r="H26" s="85">
         <f t="shared" si="2"/>
-        <v>16.247468980462308</v>
+        <v>13.580643484774132</v>
       </c>
       <c r="I26" s="84">
         <f t="shared" si="2"/>
-        <v>14.919039674343258</v>
+        <v>12.324596721227097</v>
       </c>
       <c r="J26" s="83">
         <f t="shared" si="2"/>
-        <v>13.544122330854142</v>
+        <v>11.152452174034023</v>
       </c>
       <c r="K26" s="85">
         <f t="shared" si="3"/>
-        <v>1.6411584828749808</v>
+        <v>1.8603621212019359</v>
       </c>
       <c r="L26" s="85">
         <f t="shared" si="3"/>
-        <v>1.5069737044791167</v>
+        <v>1.6883009207160407</v>
       </c>
       <c r="M26" s="85">
         <f t="shared" si="3"/>
-        <v>1.3680931647327415</v>
+        <v>1.5277331745252087</v>
       </c>
       <c r="N26" s="84">
         <f t="shared" si="4"/>
-        <v>7.944546329748345</v>
+        <v>6.9630187919835116</v>
       </c>
       <c r="O26" s="84">
         <f t="shared" si="4"/>
-        <v>7.0748586961857631</v>
+        <v>6.3677839297020968</v>
       </c>
       <c r="P26" s="83">
         <f t="shared" si="4"/>
-        <v>6.8157368768444204</v>
+        <v>6.0871753422195942</v>
       </c>
       <c r="Q26" s="46"/>
       <c r="R26" s="46"/>
@@ -9189,55 +9149,55 @@
       </c>
       <c r="D30" s="74">
         <f t="shared" ref="D30:J30" si="5">AVERAGE(D24:D27)</f>
-        <v>4.9407356426868105</v>
+        <v>4.8265499865312913</v>
       </c>
       <c r="E30" s="74">
         <f t="shared" si="5"/>
-        <v>0.90673404948175218</v>
+        <v>0.88080220533852693</v>
       </c>
       <c r="F30" s="73">
         <f t="shared" si="5"/>
-        <v>0.88051618536888221</v>
+        <v>0.85433061371006502</v>
       </c>
       <c r="G30" s="72">
         <f t="shared" si="5"/>
-        <v>0.84121089560122719</v>
+        <v>0.81626472116169591</v>
       </c>
       <c r="H30" s="71">
         <f t="shared" si="5"/>
-        <v>20.583098696841752</v>
+        <v>19.916392322919709</v>
       </c>
       <c r="I30" s="70">
         <f t="shared" si="5"/>
-        <v>17.97841225395662</v>
+        <v>17.32980151567758</v>
       </c>
       <c r="J30" s="69">
         <f t="shared" si="5"/>
-        <v>16.097154126778644</v>
+        <v>15.499236587573616</v>
       </c>
       <c r="K30" s="71">
         <f>AVERAGE(K24,K26:K26)</f>
-        <v>5.6610394986854331</v>
+        <v>5.7706413178489102</v>
       </c>
       <c r="L30" s="71">
         <f>AVERAGE(L24,L26:L26)</f>
-        <v>5.1329970443209225</v>
+        <v>5.223660652439384</v>
       </c>
       <c r="M30" s="71">
         <f>AVERAGE(M24,M26:M26)</f>
-        <v>4.670149065051997</v>
+        <v>4.7499690699482304</v>
       </c>
       <c r="N30" s="71">
         <f>AVERAGE(N24:N27)</f>
-        <v>11.257955312916412</v>
+        <v>11.012573428475203</v>
       </c>
       <c r="O30" s="70">
         <f>AVERAGE(O24:O27)</f>
-        <v>10.864750293299371</v>
+        <v>10.687981601678455</v>
       </c>
       <c r="P30" s="69">
         <f>AVERAGE(P24:P27)</f>
-        <v>10.046546745625488</v>
+        <v>9.8644063619692801</v>
       </c>
       <c r="Q30" s="46"/>
       <c r="R30" s="46"/>
@@ -9266,31 +9226,31 @@
       </c>
       <c r="H31" s="65">
         <f t="shared" si="6"/>
-        <v>20.874689889338669</v>
+        <v>19.541277141494579</v>
       </c>
       <c r="I31" s="64">
         <f t="shared" si="6"/>
-        <v>17.885984083091049</v>
+        <v>16.588762606532971</v>
       </c>
       <c r="J31" s="63">
         <f t="shared" si="6"/>
-        <v>15.495680023271554</v>
+        <v>14.299844944861494</v>
       </c>
       <c r="K31" s="65">
         <f>MEDIAN(K24,K26:K26)</f>
-        <v>5.6610394986854322</v>
+        <v>5.7706413178489102</v>
       </c>
       <c r="L31" s="65">
         <f>MEDIAN(L24,L26:L26)</f>
-        <v>5.1329970443209216</v>
+        <v>5.2236606524393849</v>
       </c>
       <c r="M31" s="65">
         <f>MEDIAN(M24,M26:M26)</f>
-        <v>4.670149065051997</v>
+        <v>4.7499690699482304</v>
       </c>
       <c r="N31" s="65">
         <f>MEDIAN(N24:N27)</f>
-        <v>8.7070258835452226</v>
+        <v>8.3397428461410374</v>
       </c>
       <c r="O31" s="64">
         <f>MEDIAN(O24:O27)</f>
@@ -9331,55 +9291,55 @@
       </c>
       <c r="D33" s="62">
         <f>D30*$J$10/$E$10</f>
-        <v>587.84912985247468</v>
+        <v>574.263311167354</v>
       </c>
       <c r="E33" s="62">
         <f t="shared" ref="E33:G34" si="7">(E30*D$19)/$E$10</f>
-        <v>351.28314521134666</v>
+        <v>341.23673769310119</v>
       </c>
       <c r="F33" s="61">
         <f t="shared" si="7"/>
-        <v>355.0710981615714</v>
+        <v>344.51167876715158</v>
       </c>
       <c r="G33" s="60">
         <f t="shared" si="7"/>
-        <v>352.84409648615576</v>
+        <v>342.38047740213113</v>
       </c>
       <c r="H33" s="62">
         <f t="shared" ref="H33:J34" si="8">H30*H$19</f>
-        <v>371.07354412357188</v>
+        <v>359.0541149450591</v>
       </c>
       <c r="I33" s="61">
         <f t="shared" si="8"/>
-        <v>374.57230880979444</v>
+        <v>361.0587894664755</v>
       </c>
       <c r="J33" s="60">
         <f t="shared" si="8"/>
-        <v>375.34265483495943</v>
+        <v>361.40081426052791</v>
       </c>
       <c r="K33" s="62">
         <f t="shared" ref="K33:M34" si="9">K30*H$19*$Q$19*100</f>
-        <v>1062.6749302971236</v>
+        <v>1083.2490855502415</v>
       </c>
       <c r="L33" s="61">
         <f t="shared" si="9"/>
-        <v>1113.5516396434066</v>
+        <v>1133.2201897330658</v>
       </c>
       <c r="M33" s="60">
         <f t="shared" si="9"/>
-        <v>1133.8734243359299</v>
+        <v>1153.2530589089422</v>
       </c>
       <c r="N33" s="62">
         <f t="shared" ref="N33:P34" si="10">(N30*N$19-($G$10-$H$10))/$E$10</f>
-        <v>426.95770885630242</v>
+        <v>416.2588732191652</v>
       </c>
       <c r="O33" s="61">
         <f t="shared" si="10"/>
-        <v>411.71739038335772</v>
+        <v>403.97916846966399</v>
       </c>
       <c r="P33" s="60">
         <f t="shared" si="10"/>
-        <v>413.08452456300239</v>
+        <v>404.43700428696667</v>
       </c>
       <c r="Q33" s="46"/>
       <c r="R33" s="46"/>
@@ -9408,31 +9368,31 @@
       </c>
       <c r="H34" s="57">
         <f t="shared" si="8"/>
-        <v>376.33037055328975</v>
+        <v>352.29151219626414</v>
       </c>
       <c r="I34" s="56">
         <f t="shared" si="8"/>
-        <v>372.64660853820544</v>
+        <v>345.61956985156758</v>
       </c>
       <c r="J34" s="55">
         <f t="shared" si="8"/>
-        <v>361.31788467703046</v>
+        <v>333.43420352816725</v>
       </c>
       <c r="K34" s="57">
         <f t="shared" si="9"/>
-        <v>1062.6749302971234</v>
+        <v>1083.2490855502415</v>
       </c>
       <c r="L34" s="56">
         <f t="shared" si="9"/>
-        <v>1113.5516396434064</v>
+        <v>1133.2201897330663</v>
       </c>
       <c r="M34" s="55">
         <f t="shared" si="9"/>
-        <v>1133.8734243359299</v>
+        <v>1153.2530589089422</v>
       </c>
       <c r="N34" s="57">
         <f t="shared" si="10"/>
-        <v>315.73525757825115</v>
+        <v>299.72143953115165</v>
       </c>
       <c r="O34" s="56">
         <f t="shared" si="10"/>
@@ -11810,10 +11770,10 @@
       <c r="E2" s="219"/>
       <c r="F2" s="219"/>
       <c r="G2" s="219"/>
-      <c r="H2" s="462" t="s">
+      <c r="H2" s="460" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="463"/>
+      <c r="I2" s="461"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="220" t="s">
@@ -11821,7 +11781,7 @@
       </c>
       <c r="B3" s="221">
         <f>Ke!D38</f>
-        <v>0.11961304285629361</v>
+        <v>0.1199027537435888</v>
       </c>
       <c r="C3" s="222"/>
       <c r="D3" s="219"/>
@@ -11829,7 +11789,7 @@
       <c r="F3" s="219"/>
       <c r="G3" s="223">
         <f ca="1">TODAY()</f>
-        <v>46061</v>
+        <v>45959</v>
       </c>
       <c r="H3" s="219" t="s">
         <v>27</v>
@@ -11853,7 +11813,7 @@
       <c r="F4" s="219"/>
       <c r="G4" s="223">
         <f ca="1">G3+365</f>
-        <v>46426</v>
+        <v>46324</v>
       </c>
       <c r="H4" s="219" t="s">
         <v>29</v>
@@ -11872,7 +11832,7 @@
       <c r="F5" s="219"/>
       <c r="G5" s="223">
         <f ca="1">G4+366</f>
-        <v>46792</v>
+        <v>46690</v>
       </c>
       <c r="H5" s="219" t="s">
         <v>30</v>
@@ -11916,9 +11876,9 @@
       <c r="A8" s="225" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="396" t="e">
+      <c r="B8" s="396">
         <f ca="1">B24</f>
-        <v>#VALUE!</v>
+        <v>272.05149552257603</v>
       </c>
       <c r="C8" s="228"/>
       <c r="D8" s="219"/>
@@ -11928,18 +11888,18 @@
         <v>32</v>
       </c>
       <c r="H8" s="233"/>
-      <c r="I8" s="234" t="e">
+      <c r="I8" s="234">
         <f ca="1">B8/$B$6-1</f>
-        <v>#VALUE!</v>
+        <v>0.12029111976023721</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1">
       <c r="A9" s="235" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="396" t="e">
+      <c r="B9" s="396">
         <f ca="1">B46</f>
-        <v>#VALUE!</v>
+        <v>289.87884277369778</v>
       </c>
       <c r="C9" s="236"/>
       <c r="D9" s="219"/>
@@ -11949,9 +11909,9 @@
         <v>35</v>
       </c>
       <c r="H9" s="237"/>
-      <c r="I9" s="238" t="e">
+      <c r="I9" s="238">
         <f ca="1">B9/B6-1</f>
-        <v>#VALUE!</v>
+        <v>0.193703025752338</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -12037,23 +11997,23 @@
       <c r="B15" s="219"/>
       <c r="C15" s="242">
         <f ca="1">MAX((C14-$G$3)/365,0)</f>
-        <v>0.30684931506849317</v>
+        <v>0.58630136986301373</v>
       </c>
       <c r="D15" s="242">
         <f ca="1">MAX((D14-$G$3)/365,0)</f>
-        <v>1.3068493150684932</v>
+        <v>1.5863013698630137</v>
       </c>
       <c r="E15" s="242">
         <f t="shared" ref="E15:G15" ca="1" si="0">MAX((E14-$G$3)/365,0)</f>
-        <v>2.3095890410958906</v>
+        <v>2.5890410958904111</v>
       </c>
       <c r="F15" s="242">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3095890410958906</v>
+        <v>3.5890410958904111</v>
       </c>
       <c r="G15" s="242">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3095890410958901</v>
+        <v>4.5890410958904111</v>
       </c>
       <c r="H15" s="242"/>
       <c r="I15" s="242"/>
@@ -12066,25 +12026,25 @@
         <v>38</v>
       </c>
       <c r="B16" s="244"/>
-      <c r="C16" s="245" t="e">
+      <c r="C16" s="245">
         <f>('Derived cash flow'!C59)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D16" s="245" t="e">
+        <v>4634.6456263393384</v>
+      </c>
+      <c r="D16" s="245">
         <f>'Derived cash flow'!D59</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E16" s="245" t="e">
+        <v>6720.3146224073289</v>
+      </c>
+      <c r="E16" s="245">
         <f>'Derived cash flow'!E59</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F16" s="245" t="e">
+        <v>6901.7994785816281</v>
+      </c>
+      <c r="F16" s="245">
         <f>'Derived cash flow'!F59</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G16" s="245" t="e">
+        <v>6955.683681815789</v>
+      </c>
+      <c r="G16" s="245">
         <f>'Derived cash flow'!G59</f>
-        <v>#VALUE!</v>
+        <v>6382.3735703889888</v>
       </c>
       <c r="H16" s="245"/>
       <c r="I16" s="245"/>
@@ -12097,25 +12057,25 @@
         <v>39</v>
       </c>
       <c r="B17" s="219"/>
-      <c r="C17" s="246" t="e">
+      <c r="C17" s="246">
         <f ca="1">(C16*C15)/((1+$B$3)^C15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D17" s="246" t="e">
+        <v>2542.7458669069347</v>
+      </c>
+      <c r="D17" s="246">
         <f ca="1">D16/((1+$B$3)^D15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E17" s="246" t="e">
+        <v>5615.323855048985</v>
+      </c>
+      <c r="E17" s="246">
         <f t="shared" ref="E17:G17" ca="1" si="1">E16/((1+$B$3)^E15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F17" s="246" t="e">
+        <v>5147.9282720350084</v>
+      </c>
+      <c r="F17" s="246">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G17" s="246" t="e">
+        <v>4632.6518209756123</v>
+      </c>
+      <c r="G17" s="246">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>3795.6988229552799</v>
       </c>
       <c r="H17" s="246"/>
       <c r="I17" s="246"/>
@@ -12173,9 +12133,9 @@
       <c r="A21" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="227" t="e">
+      <c r="B21" s="227">
         <f>G16*(1+B19)/(B3-B19)</f>
-        <v>#VALUE!</v>
+        <v>71391.54990573485</v>
       </c>
       <c r="C21" s="250"/>
       <c r="D21" s="251" t="s">
@@ -12194,9 +12154,9 @@
       <c r="A22" s="244" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="252" t="e">
+      <c r="B22" s="252">
         <f ca="1">B21/(1+B3)^(G15)</f>
-        <v>#VALUE!</v>
+        <v>42457.687403847049</v>
       </c>
       <c r="C22" s="227"/>
       <c r="D22" s="251"/>
@@ -12213,9 +12173,9 @@
       <c r="A23" s="219" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="227" t="e">
+      <c r="B23" s="227">
         <f ca="1">SUM(C17:G17)+B22</f>
-        <v>#VALUE!</v>
+        <v>64192.036041768872</v>
       </c>
       <c r="C23" s="227"/>
       <c r="D23" s="251"/>
@@ -12232,9 +12192,9 @@
       <c r="A24" s="253" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="254" t="e">
+      <c r="B24" s="254">
         <f ca="1">B23/B4</f>
-        <v>#VALUE!</v>
+        <v>272.05149552257603</v>
       </c>
       <c r="C24" s="239"/>
       <c r="D24" s="239"/>
@@ -12265,9 +12225,9 @@
     </row>
     <row r="26" spans="1:12" ht="16.2" thickBot="1">
       <c r="A26" s="219"/>
-      <c r="B26" s="256" t="e">
+      <c r="B26" s="256">
         <f ca="1">B24</f>
-        <v>#VALUE!</v>
+        <v>272.05149552257603</v>
       </c>
       <c r="C26" s="257">
         <f>D26-L27</f>
@@ -12306,29 +12266,29 @@
       <c r="A27" s="219"/>
       <c r="B27" s="259">
         <f>B28+L27</f>
-        <v>0.13461304285629361</v>
-      </c>
-      <c r="C27" s="260" t="e">
+        <v>0.13490275374358882</v>
+      </c>
+      <c r="C27" s="260">
         <f t="dataTable" ref="C27:I33" dt2D="1" dtr="1" r1="B19" r2="B3" ca="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D27" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E27" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F27" s="262" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G27" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H27" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I27" s="263" t="e">
-        <v>#VALUE!</v>
+        <v>214.68367075631596</v>
+      </c>
+      <c r="D27" s="261">
+        <v>220.70975336967263</v>
+      </c>
+      <c r="E27" s="261">
+        <v>227.27434664623996</v>
+      </c>
+      <c r="F27" s="262">
+        <v>234.45301140802965</v>
+      </c>
+      <c r="G27" s="261">
+        <v>242.33613846333614</v>
+      </c>
+      <c r="H27" s="261">
+        <v>251.03277460386082</v>
+      </c>
+      <c r="I27" s="263">
+        <v>260.67569752973998</v>
       </c>
       <c r="J27" s="46"/>
       <c r="K27" s="46"/>
@@ -12340,28 +12300,28 @@
       <c r="A28" s="219"/>
       <c r="B28" s="259">
         <f>B29+L27</f>
-        <v>0.1296130428562936</v>
-      </c>
-      <c r="C28" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D28" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E28" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F28" s="266" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G28" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H28" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I28" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.12990275374358881</v>
+      </c>
+      <c r="C28" s="264">
+        <v>223.78936323299362</v>
+      </c>
+      <c r="D28" s="265">
+        <v>230.45881454911731</v>
+      </c>
+      <c r="E28" s="265">
+        <v>237.75214608184615</v>
+      </c>
+      <c r="F28" s="266">
+        <v>245.76119247651889</v>
+      </c>
+      <c r="G28" s="265">
+        <v>254.59674235899388</v>
+      </c>
+      <c r="H28" s="265">
+        <v>264.39369432384029</v>
+      </c>
+      <c r="I28" s="267">
+        <v>275.31799283903337</v>
       </c>
       <c r="J28" s="46"/>
       <c r="K28" s="46"/>
@@ -12371,28 +12331,28 @@
       <c r="A29" s="219"/>
       <c r="B29" s="259">
         <f>B30+L27</f>
-        <v>0.12461304285629361</v>
-      </c>
-      <c r="C29" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D29" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E29" s="397" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F29" s="398" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G29" s="399" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H29" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I29" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.12490275374358881</v>
+      </c>
+      <c r="C29" s="264">
+        <v>233.70567188329358</v>
+      </c>
+      <c r="D29" s="265">
+        <v>241.11602258228569</v>
+      </c>
+      <c r="E29" s="397">
+        <v>249.25357155872942</v>
+      </c>
+      <c r="F29" s="398">
+        <v>258.23088500646742</v>
+      </c>
+      <c r="G29" s="399">
+        <v>268.18502592477125</v>
+      </c>
+      <c r="H29" s="265">
+        <v>279.28460130740439</v>
+      </c>
+      <c r="I29" s="267">
+        <v>291.73939063282904</v>
       </c>
       <c r="J29" s="46"/>
       <c r="K29" s="46"/>
@@ -12404,28 +12364,28 @@
       </c>
       <c r="B30" s="268">
         <f>Ke!D38</f>
-        <v>0.11961304285629361</v>
-      </c>
-      <c r="C30" s="269" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D30" s="270" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E30" s="400" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F30" s="401" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G30" s="402" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H30" s="270" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I30" s="271" t="e">
-        <v>#VALUE!</v>
+        <v>0.1199027537435888</v>
+      </c>
+      <c r="C30" s="269">
+        <v>244.54622843629048</v>
+      </c>
+      <c r="D30" s="270">
+        <v>252.81492807007112</v>
+      </c>
+      <c r="E30" s="400">
+        <v>261.93692643008393</v>
+      </c>
+      <c r="F30" s="401">
+        <v>272.05149552257603</v>
+      </c>
+      <c r="G30" s="402">
+        <v>283.32995973424187</v>
+      </c>
+      <c r="H30" s="270">
+        <v>295.98547950218057</v>
+      </c>
+      <c r="I30" s="271">
+        <v>310.28665162349722</v>
       </c>
       <c r="J30" s="46"/>
       <c r="K30" s="46"/>
@@ -12435,28 +12395,28 @@
       <c r="A31" s="219"/>
       <c r="B31" s="259">
         <f>B30-L27</f>
-        <v>0.1146130428562936</v>
-      </c>
-      <c r="C31" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D31" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E31" s="403" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F31" s="404" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G31" s="405" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H31" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I31" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.1149027537435888</v>
+      </c>
+      <c r="C31" s="264">
+        <v>256.44696281023215</v>
+      </c>
+      <c r="D31" s="265">
+        <v>265.71664107901745</v>
+      </c>
+      <c r="E31" s="403">
+        <v>275.99495922976399</v>
+      </c>
+      <c r="F31" s="404">
+        <v>287.45601529248438</v>
+      </c>
+      <c r="G31" s="405">
+        <v>300.31642064919816</v>
+      </c>
+      <c r="H31" s="265">
+        <v>314.84912052472635</v>
+      </c>
+      <c r="I31" s="267">
+        <v>331.40298080356155</v>
       </c>
       <c r="J31" s="46"/>
       <c r="K31" s="46"/>
@@ -12466,28 +12426,28 @@
       <c r="A32" s="219"/>
       <c r="B32" s="259">
         <f>B31-L27</f>
-        <v>0.1096130428562936</v>
-      </c>
-      <c r="C32" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E32" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F32" s="266" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G32" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H32" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I32" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.10990275374358879</v>
+      </c>
+      <c r="C32" s="264">
+        <v>269.57185569116587</v>
+      </c>
+      <c r="D32" s="265">
+        <v>280.01732788571667</v>
+      </c>
+      <c r="E32" s="265">
+        <v>291.66477260065159</v>
+      </c>
+      <c r="F32" s="266">
+        <v>304.73432392159879</v>
+      </c>
+      <c r="G32" s="265">
+        <v>319.50336592197255</v>
+      </c>
+      <c r="H32" s="265">
+        <v>336.32643801596998</v>
+      </c>
+      <c r="I32" s="267">
+        <v>355.66406611142486</v>
       </c>
       <c r="J32" s="46"/>
       <c r="K32" s="46"/>
@@ -12497,28 +12457,28 @@
       <c r="A33" s="219"/>
       <c r="B33" s="259">
         <f>B32-L27</f>
-        <v>0.10461304285629359</v>
-      </c>
-      <c r="C33" s="272" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D33" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E33" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F33" s="274" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G33" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H33" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I33" s="275" t="e">
-        <v>#VALUE!</v>
+        <v>0.10490275374358879</v>
+      </c>
+      <c r="C33" s="272">
+        <v>284.12056893120854</v>
+      </c>
+      <c r="D33" s="273">
+        <v>295.95829569127898</v>
+      </c>
+      <c r="E33" s="273">
+        <v>309.241361737148</v>
+      </c>
+      <c r="F33" s="274">
+        <v>324.25168271203546</v>
+      </c>
+      <c r="G33" s="273">
+        <v>341.34959007178026</v>
+      </c>
+      <c r="H33" s="273">
+        <v>361.00313324664779</v>
+      </c>
+      <c r="I33" s="275">
+        <v>383.83158254221473</v>
       </c>
       <c r="J33" s="46"/>
       <c r="K33" s="46"/>
@@ -12622,19 +12582,19 @@
       </c>
       <c r="D39" s="242">
         <f ca="1">MAX((D38-$G$4)/365,0)</f>
-        <v>0.30684931506849317</v>
+        <v>0.58630136986301373</v>
       </c>
       <c r="E39" s="242">
         <f t="shared" ref="E39:G39" ca="1" si="4">MAX((E38-$G$4)/365,0)</f>
-        <v>1.3095890410958904</v>
+        <v>1.5890410958904109</v>
       </c>
       <c r="F39" s="242">
         <f t="shared" ca="1" si="4"/>
-        <v>2.3095890410958906</v>
+        <v>2.5890410958904111</v>
       </c>
       <c r="G39" s="242">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3095890410958906</v>
+        <v>3.5890410958904111</v>
       </c>
       <c r="H39" s="242"/>
       <c r="I39" s="242"/>
@@ -12650,21 +12610,21 @@
       <c r="C40" s="252">
         <v>0</v>
       </c>
-      <c r="D40" s="252" t="e">
+      <c r="D40" s="252">
         <f ca="1">D16*D39</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E40" s="252" t="e">
+        <v>3940.1296690278587</v>
+      </c>
+      <c r="E40" s="252">
         <f t="shared" ref="E40:G40" si="5">E16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F40" s="252" t="e">
+        <v>6901.7994785816281</v>
+      </c>
+      <c r="F40" s="252">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G40" s="252" t="e">
+        <v>6955.683681815789</v>
+      </c>
+      <c r="G40" s="252">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>6382.3735703889888</v>
       </c>
       <c r="H40" s="252"/>
       <c r="I40" s="252"/>
@@ -12681,21 +12641,21 @@
         <f ca="1">(C40*C39)/((1+$B$3)^C39)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="246" t="e">
+      <c r="D41" s="246">
         <f ca="1">D40/((1+$B$3)^D39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E41" s="246" t="e">
+        <v>3687.0245555186975</v>
+      </c>
+      <c r="E41" s="246">
         <f ca="1">E40/((1+$B$3)^E39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F41" s="246" t="e">
+        <v>5765.179047926481</v>
+      </c>
+      <c r="F41" s="246">
         <f ca="1">F40/((1+$B$3)^F39)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G41" s="246" t="e">
+        <v>5188.11953144584</v>
+      </c>
+      <c r="G41" s="246">
         <f ca="1">G40/((1+$B$3)^G39)</f>
-        <v>#VALUE!</v>
+        <v>4250.8135642089164</v>
       </c>
       <c r="H41" s="246"/>
       <c r="I41" s="246"/>
@@ -12721,9 +12681,9 @@
       <c r="A43" s="219" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="227" t="e">
+      <c r="B43" s="227">
         <f>G40*(1+B19)/(B3-B19)</f>
-        <v>#VALUE!</v>
+        <v>71391.54990573485</v>
       </c>
       <c r="C43" s="251"/>
       <c r="D43" s="227"/>
@@ -12740,9 +12700,9 @@
       <c r="A44" s="244" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="252" t="e">
+      <c r="B44" s="252">
         <f ca="1">B43/(1+B3)^G39</f>
-        <v>#VALUE!</v>
+        <v>47548.481041152794</v>
       </c>
       <c r="C44" s="251"/>
       <c r="D44" s="227"/>
@@ -12759,9 +12719,9 @@
       <c r="A45" s="219" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="227" t="e">
+      <c r="B45" s="227">
         <f ca="1">SUM(D41:H41)+B44</f>
-        <v>#VALUE!</v>
+        <v>66439.617740252725</v>
       </c>
       <c r="C45" s="251"/>
       <c r="D45" s="227"/>
@@ -12778,9 +12738,9 @@
       <c r="A46" s="253" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="278" t="e">
+      <c r="B46" s="278">
         <f ca="1">B45/I4</f>
-        <v>#VALUE!</v>
+        <v>289.87884277369778</v>
       </c>
       <c r="C46" s="279"/>
       <c r="D46" s="279"/>
@@ -12811,9 +12771,9 @@
     </row>
     <row r="48" spans="1:12" ht="16.2" thickBot="1">
       <c r="A48" s="219"/>
-      <c r="B48" s="256" t="e">
+      <c r="B48" s="256">
         <f ca="1">B46</f>
-        <v>#VALUE!</v>
+        <v>289.87884277369778</v>
       </c>
       <c r="C48" s="257">
         <f>D48-$L$26</f>
@@ -12850,29 +12810,29 @@
       <c r="A49" s="280"/>
       <c r="B49" s="259">
         <f>B50+$L$27</f>
-        <v>0.13461304285629361</v>
-      </c>
-      <c r="C49" s="260" t="e">
+        <v>0.13490275374358882</v>
+      </c>
+      <c r="C49" s="260">
         <f t="dataTable" ref="C49:I55" dt2D="1" dtr="1" r1="B19" r2="B3" ca="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D49" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E49" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F49" s="262" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G49" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H49" s="261" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I49" s="263" t="e">
-        <v>#VALUE!</v>
+        <v>227.07306922110448</v>
+      </c>
+      <c r="D49" s="261">
+        <v>234.11372574722003</v>
+      </c>
+      <c r="E49" s="261">
+        <v>241.78355861534476</v>
+      </c>
+      <c r="F49" s="262">
+        <v>250.17085035141622</v>
+      </c>
+      <c r="G49" s="261">
+        <v>259.38121029987133</v>
+      </c>
+      <c r="H49" s="261">
+        <v>269.5420447800231</v>
+      </c>
+      <c r="I49" s="263">
+        <v>280.8084864445363</v>
       </c>
       <c r="J49" s="46"/>
       <c r="K49" s="46"/>
@@ -12882,28 +12842,28 @@
       <c r="A50" s="280"/>
       <c r="B50" s="259">
         <f>B51+$L$27</f>
-        <v>0.1296130428562936</v>
-      </c>
-      <c r="C50" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E50" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F50" s="266" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G50" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H50" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I50" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.12990275374358881</v>
+      </c>
+      <c r="C50" s="264">
+        <v>236.5534981536095</v>
+      </c>
+      <c r="D50" s="265">
+        <v>244.31151290153474</v>
+      </c>
+      <c r="E50" s="265">
+        <v>252.79523531144713</v>
+      </c>
+      <c r="F50" s="266">
+        <v>262.1114889433577</v>
+      </c>
+      <c r="G50" s="265">
+        <v>272.38914493712082</v>
+      </c>
+      <c r="H50" s="265">
+        <v>283.78511954214542</v>
+      </c>
+      <c r="I50" s="267">
+        <v>296.49244207506752</v>
       </c>
       <c r="J50" s="46"/>
       <c r="K50" s="46"/>
@@ -12913,28 +12873,28 @@
       <c r="A51" s="280"/>
       <c r="B51" s="259">
         <f>B52+$L$27</f>
-        <v>0.12461304285629361</v>
-      </c>
-      <c r="C51" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D51" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E51" s="397" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F51" s="398" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G51" s="399" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H51" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I51" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.12490275374358881</v>
+      </c>
+      <c r="C51" s="264">
+        <v>246.87878845044642</v>
+      </c>
+      <c r="D51" s="265">
+        <v>255.46048529453003</v>
+      </c>
+      <c r="E51" s="397">
+        <v>264.88432786371118</v>
+      </c>
+      <c r="F51" s="398">
+        <v>275.28067556872344</v>
+      </c>
+      <c r="G51" s="399">
+        <v>286.80825680935072</v>
+      </c>
+      <c r="H51" s="265">
+        <v>299.6623301050675</v>
+      </c>
+      <c r="I51" s="267">
+        <v>314.08583455031061</v>
       </c>
       <c r="J51" s="46"/>
       <c r="K51" s="46"/>
@@ -12946,28 +12906,28 @@
       </c>
       <c r="B52" s="281">
         <f>Ke!D38</f>
-        <v>0.11961304285629361</v>
-      </c>
-      <c r="C52" s="269" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D52" s="270" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E52" s="400" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F52" s="401" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G52" s="402" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H52" s="270" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I52" s="271" t="e">
-        <v>#VALUE!</v>
+        <v>0.1199027537435888</v>
+      </c>
+      <c r="C52" s="269">
+        <v>258.16742888056518</v>
+      </c>
+      <c r="D52" s="270">
+        <v>267.70059049729252</v>
+      </c>
+      <c r="E52" s="400">
+        <v>278.21753856470747</v>
+      </c>
+      <c r="F52" s="401">
+        <v>289.87884277369778</v>
+      </c>
+      <c r="G52" s="402">
+        <v>302.8820266938186</v>
+      </c>
+      <c r="H52" s="270">
+        <v>317.47284757677346</v>
+      </c>
+      <c r="I52" s="271">
+        <v>333.96097644581204</v>
       </c>
       <c r="J52" s="46"/>
       <c r="K52" s="46"/>
@@ -12977,28 +12937,28 @@
       <c r="A53" s="280"/>
       <c r="B53" s="259">
         <f>B52-$L$27</f>
-        <v>0.1146130428562936</v>
-      </c>
-      <c r="C53" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D53" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E53" s="403" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F53" s="404" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G53" s="405" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H53" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I53" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.1149027537435888</v>
+      </c>
+      <c r="C53" s="264">
+        <v>270.561161823323</v>
+      </c>
+      <c r="D53" s="265">
+        <v>281.20065832508362</v>
+      </c>
+      <c r="E53" s="403">
+        <v>292.99784554538837</v>
+      </c>
+      <c r="F53" s="404">
+        <v>306.15254869149601</v>
+      </c>
+      <c r="G53" s="405">
+        <v>320.91338869440466</v>
+      </c>
+      <c r="H53" s="265">
+        <v>337.59364501004052</v>
+      </c>
+      <c r="I53" s="267">
+        <v>356.59373686008706</v>
       </c>
       <c r="J53" s="46"/>
       <c r="K53" s="46"/>
@@ -13008,28 +12968,28 @@
       <c r="A54" s="280"/>
       <c r="B54" s="259">
         <f>B53-$L$27</f>
-        <v>0.1096130428562936</v>
-      </c>
-      <c r="C54" s="264" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D54" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E54" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F54" s="266" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G54" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H54" s="265" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I54" s="267" t="e">
-        <v>#VALUE!</v>
+        <v>0.10990275374358879</v>
+      </c>
+      <c r="C54" s="264">
+        <v>284.23098242702986</v>
+      </c>
+      <c r="D54" s="265">
+        <v>296.16625751626395</v>
+      </c>
+      <c r="E54" s="265">
+        <v>309.47493846147927</v>
+      </c>
+      <c r="F54" s="266">
+        <v>324.40855633944784</v>
+      </c>
+      <c r="G54" s="265">
+        <v>341.28405758972855</v>
+      </c>
+      <c r="H54" s="265">
+        <v>360.50654840183608</v>
+      </c>
+      <c r="I54" s="267">
+        <v>382.60223795936128</v>
       </c>
       <c r="J54" s="46"/>
       <c r="K54" s="46"/>
@@ -13039,28 +12999,28 @@
       <c r="A55" s="280"/>
       <c r="B55" s="259">
         <f>B54-$L$27</f>
-        <v>0.10461304285629359</v>
-      </c>
-      <c r="C55" s="272" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D55" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E55" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F55" s="274" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G55" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H55" s="273" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I55" s="275" t="e">
-        <v>#VALUE!</v>
+        <v>0.10490275374358879</v>
+      </c>
+      <c r="C55" s="272">
+        <v>299.385096082796</v>
+      </c>
+      <c r="D55" s="273">
+        <v>312.85026464019666</v>
+      </c>
+      <c r="E55" s="273">
+        <v>327.95947664448244</v>
+      </c>
+      <c r="F55" s="274">
+        <v>345.0334052900817</v>
+      </c>
+      <c r="G55" s="273">
+        <v>364.48192013115363</v>
+      </c>
+      <c r="H55" s="273">
+        <v>386.83741768262496</v>
+      </c>
+      <c r="I55" s="275">
+        <v>412.80430506726435</v>
       </c>
       <c r="J55" s="46"/>
       <c r="K55" s="46"/>
@@ -13383,7 +13343,7 @@
       </c>
       <c r="C15" s="318"/>
       <c r="D15" s="302">
-        <v>252.71</v>
+        <v>249.31</v>
       </c>
       <c r="E15" s="292"/>
       <c r="F15" s="296" t="s">
@@ -13434,7 +13394,7 @@
       <c r="C17" s="318"/>
       <c r="D17" s="285">
         <f>D15/D16</f>
-        <v>14.01608430393788</v>
+        <v>13.827509706045479</v>
       </c>
       <c r="E17" s="283"/>
       <c r="F17" s="296" t="s">
@@ -13506,7 +13466,7 @@
       <c r="C19" s="318"/>
       <c r="D19" s="299">
         <f>((1+D18)/(D17))+D18</f>
-        <v>0.18290056784456493</v>
+        <v>0.18397488067065099</v>
       </c>
       <c r="E19" s="283"/>
       <c r="F19" s="300" t="s">
@@ -13544,7 +13504,7 @@
       <c r="C20" s="318"/>
       <c r="D20" s="304">
         <f>(D19-D8)/D10</f>
-        <v>1.1799185398058605</v>
+        <v>1.1888327209534051</v>
       </c>
       <c r="E20" s="283"/>
       <c r="F20" s="300" t="s">
@@ -13948,7 +13908,7 @@
       <c r="C34" s="298"/>
       <c r="D34" s="309">
         <f>$D$8+D20*$D$33</f>
-        <v>0.11739470508738094</v>
+        <v>0.11797412686197134</v>
       </c>
       <c r="E34" s="310">
         <v>0.5</v>
@@ -14029,7 +13989,7 @@
       <c r="C38" s="298"/>
       <c r="D38" s="299">
         <f>SUMPRODUCT(D34:D36,E34:E36)</f>
-        <v>0.11961304285629361</v>
+        <v>0.1199027537435888</v>
       </c>
       <c r="E38" s="283"/>
       <c r="F38" s="300" t="s">
@@ -14162,25 +14122,25 @@
       <c r="G4">
         <v>75304</v>
       </c>
-      <c r="J4" s="158" t="e">
+      <c r="J4" s="158">
         <f>J30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K4" s="158" t="e">
+        <v>77338.698447978022</v>
+      </c>
+      <c r="K4" s="158">
         <f t="shared" ref="K4:N4" si="0">K30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L4" s="158" t="e">
+        <v>78695.626632931686</v>
+      </c>
+      <c r="L4" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M4" s="158" t="e">
+        <v>80336.672785730363</v>
+      </c>
+      <c r="M4" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N4" s="158" t="e">
+        <v>81896.23404559218</v>
+      </c>
+      <c r="N4" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>83495.330030771467</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -14292,25 +14252,25 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="159" t="e">
+      <c r="J7" s="159">
         <f>SUM(J4:J6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="159" t="e">
+        <v>89785.398913488418</v>
+      </c>
+      <c r="K7" s="159">
         <f t="shared" ref="K7:N7" si="4">SUM(K4:K6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L7" s="159" t="e">
+        <v>91440.331554504242</v>
+      </c>
+      <c r="L7" s="159">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M7" s="159" t="e">
+        <v>93465.763173656815</v>
+      </c>
+      <c r="M7" s="159">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N7" s="159" t="e">
+        <v>95421.303194072956</v>
+      </c>
+      <c r="N7" s="159">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v>97428.320896841324</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -14586,25 +14546,25 @@
         <f>SUM(G16:G17)</f>
         <v>14598</v>
       </c>
-      <c r="J18" s="158" t="e">
+      <c r="J18" s="158">
         <f>J60*J43/1000</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K18" s="158" t="e">
+        <v>14857.883758079999</v>
+      </c>
+      <c r="K18" s="158">
         <f t="shared" ref="K18:N18" si="11">K60*K43/1000</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L18" s="158" t="e">
+        <v>15003.491018909182</v>
+      </c>
+      <c r="L18" s="158">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M18" s="158" t="e">
+        <v>15303.560839287366</v>
+      </c>
+      <c r="M18" s="158">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N18" s="158" t="e">
+        <v>15765.728376633846</v>
+      </c>
+      <c r="N18" s="158">
         <f t="shared" si="11"/>
-        <v>#VALUE!</v>
+        <v>16241.853373608186</v>
       </c>
       <c r="P18" s="154"/>
       <c r="Q18" t="s">
@@ -14679,25 +14639,25 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="159" t="e">
+      <c r="J20" s="159">
         <f t="shared" ref="J20:N20" si="14">J19+J18+J15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K20" s="159" t="e">
+        <v>70637.895783610045</v>
+      </c>
+      <c r="K20" s="159">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L20" s="159" t="e">
+        <v>71751.565744645734</v>
+      </c>
+      <c r="L20" s="159">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M20" s="159" t="e">
+        <v>73148.147982489245</v>
+      </c>
+      <c r="M20" s="159">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N20" s="159" t="e">
+        <v>74467.724452747279</v>
+      </c>
+      <c r="N20" s="159">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>75817.360298900618</v>
       </c>
       <c r="P20" s="154"/>
     </row>
@@ -14958,48 +14918,48 @@
         <f>G28+G26+G20</f>
         <v>75304</v>
       </c>
-      <c r="J30" s="158" t="e">
+      <c r="J30" s="158">
         <f>J28+J26+J20</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K30" s="158" t="e">
+        <v>77338.698447978022</v>
+      </c>
+      <c r="K30" s="158">
         <f t="shared" ref="K30:M30" si="20">K28+K26+K20</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L30" s="158" t="e">
+        <v>78695.626632931686</v>
+      </c>
+      <c r="L30" s="158">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M30" s="158" t="e">
+        <v>80336.672785730363</v>
+      </c>
+      <c r="M30" s="158">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N30" s="158" t="e">
+        <v>81896.23404559218</v>
+      </c>
+      <c r="N30" s="158">
         <f>N28+N26+N20</f>
-        <v>#VALUE!</v>
+        <v>83495.330030771467</v>
       </c>
       <c r="P30" s="154"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="J31" s="162" t="e">
+      <c r="J31" s="162">
         <f>(J30-G30)/G30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K31" s="176" t="e">
+        <v>2.7019792414453708E-2</v>
+      </c>
+      <c r="K31" s="176">
         <f>(K30-J30)/J30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L31" s="176" t="e">
+        <v>1.7545267921290443E-2</v>
+      </c>
+      <c r="L31" s="176">
         <f t="shared" ref="L31:M31" si="21">(L30-K30)/K30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M31" s="176" t="e">
+        <v>2.0853079427821091E-2</v>
+      </c>
+      <c r="M31" s="176">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N31" s="176" t="e">
+        <v>1.9412818651593836E-2</v>
+      </c>
+      <c r="N31" s="176">
         <f>(N30-M30)/M30</f>
-        <v>#VALUE!</v>
+        <v>1.9525879349825286E-2</v>
       </c>
       <c r="P31" s="154"/>
     </row>
@@ -15160,25 +15120,25 @@
       </c>
       <c r="H36" s="345"/>
       <c r="I36" s="345"/>
-      <c r="J36" s="346" t="e">
+      <c r="J36" s="346">
         <f t="shared" ref="J36:N36" si="27">J89</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K36" s="346" t="e">
+        <v>89241.194618956433</v>
+      </c>
+      <c r="K36" s="346">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L36" s="346" t="e">
+        <v>90885.188753652168</v>
+      </c>
+      <c r="L36" s="346">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M36" s="346" t="e">
+        <v>92899.462002507586</v>
+      </c>
+      <c r="M36" s="346">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N36" s="346" t="e">
+        <v>94849.339011212229</v>
+      </c>
+      <c r="N36" s="346">
         <f t="shared" si="27"/>
-        <v>#VALUE!</v>
+        <v>96850.637072152022</v>
       </c>
       <c r="P36" s="154"/>
     </row>
@@ -15190,13 +15150,13 @@
       <c r="G37" s="158"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="E39" s="464" t="s">
+      <c r="E39" s="462" t="s">
         <v>152</v>
       </c>
-      <c r="F39" s="464"/>
-      <c r="G39" s="464"/>
-      <c r="H39" s="464"/>
-      <c r="I39" s="464"/>
+      <c r="F39" s="462"/>
+      <c r="G39" s="462"/>
+      <c r="H39" s="462"/>
+      <c r="I39" s="462"/>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
@@ -15780,25 +15740,25 @@
         <v>1080</v>
       </c>
       <c r="I58" s="323"/>
-      <c r="J58" s="323" t="e">
+      <c r="J58" s="323">
         <f>G58*(1+J117)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K58" s="323" t="e">
+        <v>1125.6299999999999</v>
+      </c>
+      <c r="K58" s="323">
         <f t="shared" ref="K58:N58" si="39">J58*(1+K117)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L58" s="323" t="e">
+        <v>1114.3736999999999</v>
+      </c>
+      <c r="L58" s="323">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M58" s="323" t="e">
+        <v>1114.3736999999999</v>
+      </c>
+      <c r="M58" s="323">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N58" s="323" t="e">
+        <v>1125.517437</v>
+      </c>
+      <c r="N58" s="323">
         <f t="shared" si="39"/>
-        <v>#VALUE!</v>
+        <v>1136.77261137</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -15874,25 +15834,25 @@
         <v>56451.600000000006</v>
       </c>
       <c r="I60" s="323"/>
-      <c r="J60" s="323" t="e">
+      <c r="J60" s="323">
         <f t="shared" si="41"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K60" s="323" t="e">
+        <v>58038.608429999993</v>
+      </c>
+      <c r="K60" s="323">
         <f t="shared" si="41"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L60" s="323" t="e">
+        <v>58607.386792613994</v>
+      </c>
+      <c r="L60" s="323">
         <f t="shared" si="41"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M60" s="323" t="e">
+        <v>59779.534528466269</v>
+      </c>
+      <c r="M60" s="323">
         <f t="shared" si="41"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N60" s="323" t="e">
+        <v>61584.876471225958</v>
+      </c>
+      <c r="N60" s="323">
         <f t="shared" si="41"/>
-        <v>#VALUE!</v>
+        <v>63444.73974065698</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -16796,25 +16756,25 @@
         <v>327229.08</v>
       </c>
       <c r="I86" s="323"/>
-      <c r="J86" s="323" t="e">
+      <c r="J86" s="323">
         <f>J83+J79+J72+J68+J64+J60+J56+J52+J48</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K86" s="323" t="e">
+        <v>331278.10398029856</v>
+      </c>
+      <c r="K86" s="323">
         <f t="shared" ref="K86:N86" si="59">K83+K79+K72+K68+K64+K60+K56+K52+K48</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L86" s="323" t="e">
+        <v>337291.12053534848</v>
+      </c>
+      <c r="L86" s="323">
         <f t="shared" si="59"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M86" s="323" t="e">
+        <v>344738.25816299353</v>
+      </c>
+      <c r="M86" s="323">
         <f t="shared" si="59"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N86" s="323" t="e">
+        <v>351921.19730873499</v>
+      </c>
+      <c r="N86" s="323">
         <f t="shared" si="59"/>
-        <v>#VALUE!</v>
+        <v>359291.96923565352</v>
       </c>
     </row>
     <row r="87" spans="1:21">
@@ -16846,25 +16806,25 @@
         <v>83116.186320000008</v>
       </c>
       <c r="I87" s="323"/>
-      <c r="J87" s="323" t="e">
+      <c r="J87" s="323">
         <f>J86*J43/1000</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K87" s="323" t="e">
+        <v>84807.194618956433</v>
+      </c>
+      <c r="K87" s="323">
         <f t="shared" ref="K87:N87" si="61">K86*K43/1000</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L87" s="323" t="e">
+        <v>86346.526857049219</v>
+      </c>
+      <c r="L87" s="323">
         <f t="shared" si="61"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M87" s="323" t="e">
+        <v>88252.994089726344</v>
+      </c>
+      <c r="M87" s="323">
         <f t="shared" si="61"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N87" s="323" t="e">
+        <v>90091.826511036154</v>
+      </c>
+      <c r="N87" s="323">
         <f t="shared" si="61"/>
-        <v>#VALUE!</v>
+        <v>91978.744124327306</v>
       </c>
     </row>
     <row r="88" spans="1:21">
@@ -16943,25 +16903,25 @@
         <v>83987.186320000008</v>
       </c>
       <c r="I89" s="323"/>
-      <c r="J89" s="323" t="e">
+      <c r="J89" s="323">
         <f>J87+J88+J74</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K89" s="323" t="e">
+        <v>89241.194618956433</v>
+      </c>
+      <c r="K89" s="323">
         <f t="shared" ref="K89:N89" si="64">K87+K88+K74</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L89" s="323" t="e">
+        <v>90885.188753652168</v>
+      </c>
+      <c r="L89" s="323">
         <f t="shared" si="64"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M89" s="323" t="e">
+        <v>92899.462002507586</v>
+      </c>
+      <c r="M89" s="323">
         <f t="shared" si="64"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N89" s="323" t="e">
+        <v>94849.339011212229</v>
+      </c>
+      <c r="N89" s="323">
         <f t="shared" si="64"/>
-        <v>#VALUE!</v>
+        <v>96850.637072152022</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>180</v>
@@ -16973,14 +16933,14 @@
       </c>
     </row>
     <row r="95" spans="1:21">
-      <c r="P95" s="465" t="s">
+      <c r="P95" s="463" t="s">
         <v>182</v>
       </c>
-      <c r="Q95" s="464"/>
-      <c r="R95" s="464"/>
-      <c r="S95" s="464"/>
-      <c r="T95" s="464"/>
-      <c r="U95" s="464"/>
+      <c r="Q95" s="462"/>
+      <c r="R95" s="462"/>
+      <c r="S95" s="462"/>
+      <c r="T95" s="462"/>
+      <c r="U95" s="462"/>
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="2" t="s">
@@ -17649,9 +17609,9 @@
         <f t="shared" si="74"/>
         <v>-5.0131926121372031E-2</v>
       </c>
-      <c r="J117" s="177" t="e">
-        <f>+CHOOSE([1]Cover!$I$14,Revenue!J118,Revenue!J119,Revenue!J120)</f>
-        <v>#VALUE!</v>
+      <c r="J117" s="177">
+        <f>+CHOOSE(Cover!$I$13,Revenue!J118,Revenue!J119,Revenue!J120)</f>
+        <v>-0.01</v>
       </c>
       <c r="K117" s="177">
         <f>+CHOOSE(Cover!$I$13,Revenue!K118,Revenue!K119,Revenue!K120)</f>
@@ -19350,25 +19310,25 @@
       <c r="G5" s="165">
         <v>22244</v>
       </c>
-      <c r="H5" s="158" t="e">
+      <c r="H5" s="158">
         <f>Revenue!J36</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="158" t="e">
+        <v>89241.194618956433</v>
+      </c>
+      <c r="I5" s="158">
         <f>Revenue!K36</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J5" s="158" t="e">
+        <v>90885.188753652168</v>
+      </c>
+      <c r="J5" s="158">
         <f>Revenue!L36</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K5" s="158" t="e">
+        <v>92899.462002507586</v>
+      </c>
+      <c r="K5" s="158">
         <f>Revenue!M36</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L5" s="158" t="e">
+        <v>94849.339011212229</v>
+      </c>
+      <c r="L5" s="158">
         <f>Revenue!N36</f>
-        <v>#VALUE!</v>
+        <v>96850.637072152022</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -19398,29 +19358,29 @@
         <f>'Operating expenses'!D79</f>
         <v>31232</v>
       </c>
-      <c r="G7" s="170" t="e">
+      <c r="G7" s="170">
         <f>'Operating expenses'!E79</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H7" s="170" t="e">
+        <v>30770.008027551223</v>
+      </c>
+      <c r="H7" s="170">
         <f>'Operating expenses'!E79</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I7" s="170" t="e">
+        <v>30770.008027551223</v>
+      </c>
+      <c r="I7" s="170">
         <f>'Operating expenses'!F79</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="170" t="e">
+        <v>30565.170527190654</v>
+      </c>
+      <c r="J7" s="170">
         <f>'Operating expenses'!G79</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="170" t="e">
+        <v>31259.894861954483</v>
+      </c>
+      <c r="K7" s="170">
         <f>'Operating expenses'!H79</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L7" s="170" t="e">
+        <v>31934.966483098731</v>
+      </c>
+      <c r="L7" s="170">
         <f>'Operating expenses'!I79</f>
-        <v>#VALUE!</v>
+        <v>32628.07053374068</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -19448,25 +19408,25 @@
       <c r="G8" s="165">
         <v>5488</v>
       </c>
-      <c r="H8" s="170" t="e">
+      <c r="H8" s="170">
         <f>'Operating expenses'!E80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I8" s="170" t="e">
+        <v>21827.31806922135</v>
+      </c>
+      <c r="I8" s="170">
         <f>'Operating expenses'!F80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="170" t="e">
+        <v>22224.878436611809</v>
+      </c>
+      <c r="J8" s="170">
         <f>'Operating expenses'!G80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="170" t="e">
+        <v>22704.681171968641</v>
+      </c>
+      <c r="K8" s="170">
         <f>'Operating expenses'!H80</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L8" s="170" t="e">
+        <v>23164.898102707433</v>
+      </c>
+      <c r="L8" s="170">
         <f>'Operating expenses'!I80</f>
-        <v>#VALUE!</v>
+        <v>23637.04252909356</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -19494,25 +19454,25 @@
       <c r="G9" s="165">
         <v>1192</v>
       </c>
-      <c r="H9" s="170" t="e">
+      <c r="H9" s="170">
         <f>'Operating expenses'!E81</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I9" s="170" t="e">
+        <v>4802.0229049207901</v>
+      </c>
+      <c r="I9" s="170">
         <f>'Operating expenses'!F81</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="170" t="e">
+        <v>5071.275683785866</v>
+      </c>
+      <c r="J9" s="170">
         <f>'Operating expenses'!G81</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K9" s="170" t="e">
+        <v>5359.9382876206082</v>
+      </c>
+      <c r="K9" s="170">
         <f>'Operating expenses'!H81</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L9" s="170" t="e">
+        <v>5666.7947806794109</v>
+      </c>
+      <c r="L9" s="170">
         <f>'Operating expenses'!I81</f>
-        <v>#VALUE!</v>
+        <v>5993.1529894377773</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -19540,25 +19500,25 @@
       <c r="G10" s="165">
         <v>1092</v>
       </c>
-      <c r="H10" s="170" t="e">
+      <c r="H10" s="170">
         <f>'Operating expenses'!E82</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I10" s="170" t="e">
+        <v>4361.6470393780701</v>
+      </c>
+      <c r="I10" s="170">
         <f>'Operating expenses'!F82</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="170" t="e">
+        <v>4333.2817135293235</v>
+      </c>
+      <c r="J10" s="170">
         <f>'Operating expenses'!G82</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="170" t="e">
+        <v>4349.0181750900065</v>
+      </c>
+      <c r="K10" s="170">
         <f>'Operating expenses'!H82</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L10" s="170" t="e">
+        <v>4430.4429629108799</v>
+      </c>
+      <c r="L10" s="170">
         <f>'Operating expenses'!I82</f>
-        <v>#VALUE!</v>
+        <v>4523.7068484238343</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -19586,25 +19546,25 @@
       <c r="G11" s="165">
         <v>873</v>
       </c>
-      <c r="H11" s="170" t="e">
+      <c r="H11" s="170">
         <f>'Operating expenses'!E83</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I11" s="170" t="e">
+        <v>3868.2323199498696</v>
+      </c>
+      <c r="I11" s="170">
         <f>'Operating expenses'!F83</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="170" t="e">
+        <v>3937.9222622672119</v>
+      </c>
+      <c r="J11" s="170">
         <f>'Operating expenses'!G83</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K11" s="170" t="e">
+        <v>4024.4012153290005</v>
+      </c>
+      <c r="K11" s="170">
         <f>'Operating expenses'!H83</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L11" s="170" t="e">
+        <v>4107.7213812113305</v>
+      </c>
+      <c r="L11" s="170">
         <f>'Operating expenses'!I83</f>
-        <v>#VALUE!</v>
+        <v>4193.2248107260393</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -19632,25 +19592,25 @@
       <c r="G12" s="165">
         <v>843</v>
       </c>
-      <c r="H12" s="170" t="e">
+      <c r="H12" s="170">
         <f>'Operating expenses'!E84</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I12" s="170" t="e">
+        <v>3236.3170649111844</v>
+      </c>
+      <c r="I12" s="170">
         <f>'Operating expenses'!F84</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="170" t="e">
+        <v>3205.0393327359229</v>
+      </c>
+      <c r="J12" s="170">
         <f>'Operating expenses'!G84</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K12" s="170" t="e">
+        <v>3276.1332193068265</v>
+      </c>
+      <c r="K12" s="170">
         <f>'Operating expenses'!H84</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L12" s="170" t="e">
+        <v>3253.1752096302848</v>
+      </c>
+      <c r="L12" s="170">
         <f>'Operating expenses'!I84</f>
-        <v>#VALUE!</v>
+        <v>3321.7484764778892</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -19768,25 +19728,25 @@
         <f>3396+45</f>
         <v>3441</v>
       </c>
-      <c r="H15" s="170" t="e">
+      <c r="H15" s="170">
         <f>'Operating expenses'!E87</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I15" s="170" t="e">
+        <v>13354.807173069039</v>
+      </c>
+      <c r="I15" s="170">
         <f>'Operating expenses'!F87</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J15" s="170" t="e">
+        <v>13535.083585959212</v>
+      </c>
+      <c r="J15" s="170">
         <f>'Operating expenses'!G87</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K15" s="170" t="e">
+        <v>13924.897348213954</v>
+      </c>
+      <c r="K15" s="170">
         <f>'Operating expenses'!H87</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L15" s="170" t="e">
+        <v>14229.398073654902</v>
+      </c>
+      <c r="L15" s="170">
         <f>'Operating expenses'!I87</f>
-        <v>#VALUE!</v>
+        <v>14544.991993516547</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -19813,29 +19773,29 @@
         <f t="shared" si="0"/>
         <v>82709</v>
       </c>
-      <c r="G16" s="166" t="e">
+      <c r="G16" s="166">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H16" s="159" t="e">
+        <v>43766.008027551223</v>
+      </c>
+      <c r="H16" s="159">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I16" s="159" t="e">
+        <v>82741.352599001533</v>
+      </c>
+      <c r="I16" s="159">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="159" t="e">
+        <v>83093.651542079984</v>
+      </c>
+      <c r="J16" s="159">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K16" s="159" t="e">
+        <v>85019.964279483509</v>
+      </c>
+      <c r="K16" s="159">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L16" s="159" t="e">
+        <v>86808.396993892966</v>
+      </c>
+      <c r="L16" s="159">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>88862.938181416335</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -19865,25 +19825,25 @@
       <c r="G17" s="165">
         <v>1186</v>
       </c>
-      <c r="H17" s="159" t="e">
+      <c r="H17" s="159">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I17" s="159" t="e">
+        <v>6499.8420199549</v>
+      </c>
+      <c r="I17" s="159">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J17" s="159" t="e">
+        <v>7791.5372115721839</v>
+      </c>
+      <c r="J17" s="159">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K17" s="159" t="e">
+        <v>7879.4977230240765</v>
+      </c>
+      <c r="K17" s="159">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L17" s="159" t="e">
+        <v>8040.942017319263</v>
+      </c>
+      <c r="L17" s="159">
         <f>L5-L16</f>
-        <v>#VALUE!</v>
+        <v>7987.6988907356863</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -19958,25 +19918,25 @@
       <c r="F20">
         <v>363</v>
       </c>
-      <c r="H20" s="158" t="e">
+      <c r="H20" s="158">
         <f>H60*'Balance sheet'!G23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I20" s="158" t="e">
+        <v>211.13957750943774</v>
+      </c>
+      <c r="I20" s="158">
         <f>I60*'Balance sheet'!H23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J20" s="158" t="e">
+        <v>215.0291738837328</v>
+      </c>
+      <c r="J20" s="158">
         <f>J60*'Balance sheet'!I23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K20" s="158" t="e">
+        <v>219.7948295270466</v>
+      </c>
+      <c r="K20" s="158">
         <f>K60*'Balance sheet'!J23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L20" s="158" t="e">
+        <v>224.40812733834474</v>
+      </c>
+      <c r="L20" s="158">
         <f>L60*'Balance sheet'!K23</f>
-        <v>#VALUE!</v>
+        <v>229.14308442695739</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -20001,25 +19961,25 @@
       <c r="G21" s="165">
         <v>60</v>
       </c>
-      <c r="H21" s="158" t="e">
+      <c r="H21" s="158">
         <f>H61*H7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I21" s="158" t="e">
+        <v>758.18862532009234</v>
+      </c>
+      <c r="I21" s="158">
         <f t="shared" ref="I21:L21" si="2">I61*I7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J21" s="158" t="e">
+        <v>753.14132527800837</v>
+      </c>
+      <c r="J21" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K21" s="158" t="e">
+        <v>770.25968572430304</v>
+      </c>
+      <c r="K21" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L21" s="158" t="e">
+        <v>786.89379332575936</v>
+      </c>
+      <c r="L21" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>803.97222914837846</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -20133,25 +20093,25 @@
         <f t="shared" si="5"/>
         <v>-52</v>
       </c>
-      <c r="H24" s="159" t="e">
+      <c r="H24" s="159">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I24" s="159" t="e">
+        <v>49.777202829530097</v>
+      </c>
+      <c r="I24" s="159">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J24" s="159" t="e">
+        <v>-59.593500838258819</v>
+      </c>
+      <c r="J24" s="159">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K24" s="159" t="e">
+        <v>-163.12148474865046</v>
+      </c>
+      <c r="K24" s="159">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L24" s="159" t="e">
+        <v>-196.07807933589606</v>
+      </c>
+      <c r="L24" s="159">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>-235.52468642466431</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -20182,25 +20142,25 @@
         <f>G17+G24</f>
         <v>1134</v>
       </c>
-      <c r="H25" s="159" t="e">
+      <c r="H25" s="159">
         <f t="shared" ref="H25:L25" si="7">H17+H24</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I25" s="159" t="e">
+        <v>6549.6192227844303</v>
+      </c>
+      <c r="I25" s="159">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J25" s="159" t="e">
+        <v>7731.9437107339254</v>
+      </c>
+      <c r="J25" s="159">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K25" s="159" t="e">
+        <v>7716.3762382754257</v>
+      </c>
+      <c r="K25" s="159">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L25" s="159" t="e">
+        <v>7844.8639379833667</v>
+      </c>
+      <c r="L25" s="159">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>7752.1742043110216</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -20225,25 +20185,25 @@
       <c r="G26" s="165">
         <v>310</v>
       </c>
-      <c r="H26" s="158" t="e">
+      <c r="H26" s="158">
         <f>H25*H66</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I26" s="158" t="e">
+        <v>1637.4048056961076</v>
+      </c>
+      <c r="I26" s="158">
         <f>I25*I66</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J26" s="158" t="e">
+        <v>1932.9859276834813</v>
+      </c>
+      <c r="J26" s="158">
         <f>J25*J66</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K26" s="158" t="e">
+        <v>1929.0940595688564</v>
+      </c>
+      <c r="K26" s="158">
         <f>K25*K66</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L26" s="158" t="e">
+        <v>1961.2159844958417</v>
+      </c>
+      <c r="L26" s="158">
         <f>L25*L66</f>
-        <v>#VALUE!</v>
+        <v>1938.0435510777554</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -20274,25 +20234,25 @@
         <f t="shared" si="8"/>
         <v>824</v>
       </c>
-      <c r="H27" s="346" t="e">
+      <c r="H27" s="346">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I27" s="346" t="e">
+        <v>4912.214417088323</v>
+      </c>
+      <c r="I27" s="346">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J27" s="346" t="e">
+        <v>5798.957783050444</v>
+      </c>
+      <c r="J27" s="346">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K27" s="346" t="e">
+        <v>5787.2821787065695</v>
+      </c>
+      <c r="K27" s="346">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L27" s="346" t="e">
+        <v>5883.6479534875252</v>
+      </c>
+      <c r="L27" s="346">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
+        <v>5814.1306532332665</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -20317,25 +20277,25 @@
       <c r="G28" s="165">
         <v>3.48</v>
       </c>
-      <c r="H28" s="158" t="e">
+      <c r="H28" s="158">
         <f>'Debt schedule'!C32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I28" s="158" t="e">
+        <v>21.630182373792703</v>
+      </c>
+      <c r="I28" s="158">
         <f>'Debt schedule'!D32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J28" s="158" t="e">
+        <v>26.68273033198566</v>
+      </c>
+      <c r="J28" s="158">
         <f>'Debt schedule'!E32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K28" s="158" t="e">
+        <v>27.820796936383854</v>
+      </c>
+      <c r="K28" s="158">
         <f>'Debt schedule'!F32</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L28" s="158" t="e">
+        <v>29.542317500941582</v>
+      </c>
+      <c r="L28" s="158">
         <f>'Debt schedule'!G32</f>
-        <v>#VALUE!</v>
+        <v>30.485164918379123</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -20394,25 +20354,25 @@
         <f>G25-G26</f>
         <v>824</v>
       </c>
-      <c r="H30" s="158" t="e">
+      <c r="H30" s="158">
         <f>H25-H26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I30" s="158" t="e">
+        <v>4912.214417088323</v>
+      </c>
+      <c r="I30" s="158">
         <f t="shared" ref="I30:L30" si="10">I25-I26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J30" s="158" t="e">
+        <v>5798.957783050444</v>
+      </c>
+      <c r="J30" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K30" s="158" t="e">
+        <v>5787.2821787065695</v>
+      </c>
+      <c r="K30" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L30" s="158" t="e">
+        <v>5883.6479534875252</v>
+      </c>
+      <c r="L30" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <v>5814.1306532332665</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -20586,25 +20546,25 @@
         <v>4089</v>
       </c>
       <c r="G36"/>
-      <c r="H36" s="158" t="e">
+      <c r="H36" s="158">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I36" s="158" t="e">
+        <v>4907.214417088323</v>
+      </c>
+      <c r="I36" s="158">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J36" s="158" t="e">
+        <v>5793.957783050444</v>
+      </c>
+      <c r="J36" s="158">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K36" s="158" t="e">
+        <v>5782.2821787065695</v>
+      </c>
+      <c r="K36" s="158">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L36" s="158" t="e">
+        <v>5878.6479534875252</v>
+      </c>
+      <c r="L36" s="158">
         <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <v>5809.1306532332665</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -20669,25 +20629,25 @@
         <v>2.6569965675709577E-3</v>
       </c>
       <c r="G41" s="167"/>
-      <c r="H41" s="154" t="e">
+      <c r="H41" s="154">
         <f>(H5-F5)/F5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I41" s="154" t="e">
+        <v>1.495797169160923E-2</v>
+      </c>
+      <c r="I41" s="154">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J41" s="154" t="e">
+        <v>1.8421919851199762E-2</v>
+      </c>
+      <c r="J41" s="154">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K41" s="154" t="e">
+        <v>2.2162832871648462E-2</v>
+      </c>
+      <c r="K41" s="154">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L41" s="154" t="e">
+        <v>2.0989109804015995E-2</v>
+      </c>
+      <c r="L41" s="154">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>2.1099757592440548E-2</v>
       </c>
       <c r="O41" s="163" t="s">
         <v>245</v>
@@ -21230,25 +21190,25 @@
         <f t="shared" si="18"/>
         <v>5.3317748606365761E-2</v>
       </c>
-      <c r="H57" s="154" t="e">
+      <c r="H57" s="154">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I57" s="154" t="e">
+        <v>7.2834547405018907E-2</v>
+      </c>
+      <c r="I57" s="154">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J57" s="154" t="e">
+        <v>8.5729449632232682E-2</v>
+      </c>
+      <c r="J57" s="154">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K57" s="154" t="e">
+        <v>8.4817474215419991E-2</v>
+      </c>
+      <c r="K57" s="154">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L57" s="154" t="e">
+        <v>8.4775941520991896E-2</v>
+      </c>
+      <c r="L57" s="154">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
+        <v>8.2474407316340009E-2</v>
       </c>
       <c r="O57" s="163"/>
     </row>
@@ -21380,9 +21340,9 @@
         <f t="shared" si="20"/>
         <v>2.2829149590163935E-2</v>
       </c>
-      <c r="G61" s="176" t="e">
+      <c r="G61" s="176">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
+        <v>1.9499507424982298E-3</v>
       </c>
       <c r="H61" s="176">
         <f>AVERAGE(B61:F61)</f>
@@ -21751,22 +21711,22 @@
       <c r="P84" s="446"/>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="466"/>
-      <c r="B85" s="466"/>
-      <c r="C85" s="466"/>
-      <c r="D85" s="466"/>
-      <c r="E85" s="466"/>
-      <c r="F85" s="466"/>
-      <c r="G85" s="466"/>
-      <c r="H85" s="466"/>
-      <c r="I85" s="466"/>
-      <c r="J85" s="466"/>
-      <c r="K85" s="466"/>
-      <c r="L85" s="466"/>
-      <c r="M85" s="466"/>
-      <c r="N85" s="466"/>
-      <c r="O85" s="466"/>
-      <c r="P85" s="466"/>
+      <c r="A85" s="464"/>
+      <c r="B85" s="464"/>
+      <c r="C85" s="464"/>
+      <c r="D85" s="464"/>
+      <c r="E85" s="464"/>
+      <c r="F85" s="464"/>
+      <c r="G85" s="464"/>
+      <c r="H85" s="464"/>
+      <c r="I85" s="464"/>
+      <c r="J85" s="464"/>
+      <c r="K85" s="464"/>
+      <c r="L85" s="464"/>
+      <c r="M85" s="464"/>
+      <c r="N85" s="464"/>
+      <c r="O85" s="464"/>
+      <c r="P85" s="464"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21841,25 +21801,25 @@
         <f>Revenue!G4</f>
         <v>75304</v>
       </c>
-      <c r="E4" s="452" t="e">
+      <c r="E4" s="452">
         <f>Revenue!J4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" s="452" t="e">
+        <v>77338.698447978022</v>
+      </c>
+      <c r="F4" s="452">
         <f>Revenue!K4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G4" s="452" t="e">
+        <v>78695.626632931686</v>
+      </c>
+      <c r="G4" s="452">
         <f>Revenue!L4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" s="452" t="e">
+        <v>80336.672785730363</v>
+      </c>
+      <c r="H4" s="452">
         <f>Revenue!M4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I4" s="452" t="e">
+        <v>81896.23404559218</v>
+      </c>
+      <c r="I4" s="452">
         <f>Revenue!N4</f>
-        <v>#VALUE!</v>
+        <v>83495.330030771467</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -21875,25 +21835,25 @@
       <c r="D5" s="189">
         <v>25091</v>
       </c>
-      <c r="E5" s="158" t="e">
+      <c r="E5" s="158">
         <f>E4*E6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F5" s="158" t="e">
+        <v>24748.383503352969</v>
+      </c>
+      <c r="F5" s="158">
         <f t="shared" ref="F5:I5" si="0">F4*F6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G5" s="158" t="e">
+        <v>24395.644256208823</v>
+      </c>
+      <c r="G5" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="158" t="e">
+        <v>24904.368563576412</v>
+      </c>
+      <c r="H5" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="158" t="e">
+        <v>25387.832554133576</v>
+      </c>
+      <c r="I5" s="158">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>25883.552309539155</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -21991,7 +21951,7 @@
       <c r="C9" s="448"/>
       <c r="D9" s="448"/>
       <c r="E9" s="154">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="F9" s="154">
         <v>0.32</v>
@@ -22019,25 +21979,25 @@
       <c r="D10" s="189">
         <v>19974</v>
       </c>
-      <c r="E10" s="158" t="e">
+      <c r="E10" s="158">
         <f>E4*E11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F10" s="158" t="e">
+        <v>20108.061596474286</v>
+      </c>
+      <c r="F10" s="158">
         <f t="shared" ref="F10:I10" si="2">F4*F11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G10" s="158" t="e">
+        <v>20460.86292456224</v>
+      </c>
+      <c r="G10" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H10" s="158" t="e">
+        <v>20887.534924289896</v>
+      </c>
+      <c r="H10" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I10" s="158" t="e">
+        <v>21293.020851853969</v>
+      </c>
+      <c r="I10" s="158">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>21708.785808000583</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -22160,25 +22120,25 @@
       <c r="D15" s="189">
         <v>3939</v>
       </c>
-      <c r="E15" s="158" t="e">
+      <c r="E15" s="158">
         <f>E4*E16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F15" s="158" t="e">
+        <v>4045.4309623205331</v>
+      </c>
+      <c r="F15" s="158">
         <f t="shared" ref="F15" si="4">E15*(1+F16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G15" s="158" t="e">
+        <v>4257.0392774243865</v>
+      </c>
+      <c r="G15" s="158">
         <f t="shared" ref="G15" si="5">F15*(1+G16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H15" s="158" t="e">
+        <v>4479.7163956886834</v>
+      </c>
+      <c r="H15" s="158">
         <f t="shared" ref="H15" si="6">G15*(1+H16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I15" s="158" t="e">
+        <v>4714.0413038292563</v>
+      </c>
+      <c r="I15" s="158">
         <f t="shared" ref="I15" si="7">H15*(1+I16)</f>
-        <v>#VALUE!</v>
+        <v>4960.6232741865206</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -22232,25 +22192,25 @@
       <c r="D17" s="189">
         <v>3722</v>
       </c>
-      <c r="E17" s="158" t="e">
+      <c r="E17" s="158">
         <f>E4*E18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F17" s="158" t="e">
+        <v>3812.0554152606251</v>
+      </c>
+      <c r="F17" s="158">
         <f t="shared" ref="F17:I17" si="10">F4*F18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G17" s="158" t="e">
+        <v>3777.3900783807212</v>
+      </c>
+      <c r="G17" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H17" s="158" t="e">
+        <v>3775.8236209293273</v>
+      </c>
+      <c r="H17" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I17" s="158" t="e">
+        <v>3849.1230001428326</v>
+      </c>
+      <c r="I17" s="158">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <v>3924.280511446259</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -22301,25 +22261,25 @@
       <c r="D19" s="189">
         <v>3316</v>
       </c>
-      <c r="E19" s="158" t="e">
+      <c r="E19" s="158">
         <f>E4*E20</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F19" s="158" t="e">
+        <v>3405.5976316463284</v>
+      </c>
+      <c r="F19" s="158">
         <f t="shared" ref="F19:I19" si="12">F4*F20</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G19" s="158" t="e">
+        <v>3465.3497545256755</v>
+      </c>
+      <c r="G19" s="158">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H19" s="158" t="e">
+        <v>3537.6129682019796</v>
+      </c>
+      <c r="H19" s="158">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I19" s="158" t="e">
+        <v>3606.2880072132111</v>
+      </c>
+      <c r="I19" s="158">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
+        <v>3676.7039517427784</v>
       </c>
       <c r="L19" s="451"/>
     </row>
@@ -22369,25 +22329,25 @@
       <c r="D21" s="189">
         <v>2799</v>
       </c>
-      <c r="E21" s="158" t="e">
+      <c r="E21" s="158">
         <f>E4*E22</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F21" s="158" t="e">
+        <v>2784.1931441272086</v>
+      </c>
+      <c r="F21" s="158">
         <f t="shared" ref="F21:I21" si="14">F4*F22</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G21" s="158" t="e">
+        <v>2754.346932152609</v>
+      </c>
+      <c r="G21" s="158">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H21" s="158" t="e">
+        <v>2811.7835475005631</v>
+      </c>
+      <c r="H21" s="158">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I21" s="158" t="e">
+        <v>2784.4719575501344</v>
+      </c>
+      <c r="I21" s="158">
         <f t="shared" si="14"/>
-        <v>#VALUE!</v>
+        <v>2838.8412210462302</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -22494,25 +22454,25 @@
       <c r="D25" s="186">
         <v>-791</v>
       </c>
-      <c r="E25" s="158" t="e">
+      <c r="E25" s="158">
         <f>E4*E26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F25" s="158" t="e">
+        <v>-812.37265579983296</v>
+      </c>
+      <c r="F25" s="158">
         <f t="shared" ref="F25:I25" si="16">F4*F26</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G25" s="158" t="e">
+        <v>-826.62595169777126</v>
+      </c>
+      <c r="G25" s="158">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H25" s="158" t="e">
+        <v>-843.8636483256231</v>
+      </c>
+      <c r="H25" s="158">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I25" s="158" t="e">
+        <v>-860.2454202972408</v>
+      </c>
+      <c r="I25" s="158">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
+        <v>-877.04246858520446</v>
       </c>
       <c r="N25" t="s">
         <v>532</v>
@@ -22561,25 +22521,25 @@
       <c r="D27" s="189">
         <v>11964</v>
       </c>
-      <c r="E27" s="158" t="e">
+      <c r="E27" s="158">
         <f>E28*E4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F27" s="158" t="e">
+        <v>12275.411794073321</v>
+      </c>
+      <c r="F27" s="158">
         <f t="shared" ref="F27:I27" si="18">F28*F4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G27" s="158" t="e">
+        <v>12400.397084089018</v>
+      </c>
+      <c r="G27" s="158">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H27" s="158" t="e">
+        <v>12724.604381452065</v>
+      </c>
+      <c r="H27" s="158">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I27" s="158" t="e">
+        <v>12958.383783397263</v>
+      </c>
+      <c r="I27" s="158">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
+        <v>13197.673708668226</v>
       </c>
       <c r="L27" s="451"/>
     </row>
@@ -22634,25 +22594,25 @@
         <f>SUM(D5:D27)</f>
         <v>70419.770875385118</v>
       </c>
-      <c r="E29" s="455" t="e">
+      <c r="E29" s="455">
         <f t="shared" ref="E29:I29" si="21">SUM(E5:E27)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F29" s="455" t="e">
+        <v>70640.242520589542</v>
+      </c>
+      <c r="F29" s="455">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G29" s="455" t="e">
+        <v>70807.853194379364</v>
+      </c>
+      <c r="G29" s="455">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H29" s="455" t="e">
+        <v>72301.028592046976</v>
+      </c>
+      <c r="H29" s="455">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I29" s="455" t="e">
+        <v>73756.362876556668</v>
+      </c>
+      <c r="I29" s="455">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>75336.865154778206</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -23353,9 +23313,9 @@
         <f t="shared" ref="I52" si="48">SUM(I34:I50)</f>
         <v>8289.7980537548501</v>
       </c>
-      <c r="L52" t="e">
+      <c r="L52">
         <f>I52/$I$90</f>
-        <v>#VALUE!</v>
+        <v>9.325264040285397E-2</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -24045,9 +24005,9 @@
         <f t="shared" ref="I75" si="88">SUM(I57:I73)</f>
         <v>5269.4583162054978</v>
       </c>
-      <c r="L75" t="e">
+      <c r="L75">
         <f>I75/$I$90</f>
-        <v>#VALUE!</v>
+        <v>5.9276582890504192E-2</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -24095,25 +24055,25 @@
         <f t="shared" si="89"/>
         <v>31232</v>
       </c>
-      <c r="E79" s="189" t="e">
+      <c r="E79" s="189">
         <f t="shared" si="89"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F79" s="189" t="e">
+        <v>30770.008027551223</v>
+      </c>
+      <c r="F79" s="189">
         <f t="shared" si="89"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G79" s="189" t="e">
+        <v>30565.170527190654</v>
+      </c>
+      <c r="G79" s="189">
         <f t="shared" si="89"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H79" s="189" t="e">
+        <v>31259.894861954483</v>
+      </c>
+      <c r="H79" s="189">
         <f t="shared" si="89"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I79" s="189" t="e">
+        <v>31934.966483098731</v>
+      </c>
+      <c r="I79" s="189">
         <f t="shared" si="89"/>
-        <v>#VALUE!</v>
+        <v>32628.07053374068</v>
       </c>
       <c r="K79" s="448"/>
     </row>
@@ -24133,25 +24093,25 @@
         <f t="shared" si="90"/>
         <v>21768</v>
       </c>
-      <c r="E80" s="189" t="e">
+      <c r="E80" s="189">
         <f t="shared" si="90"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F80" s="189" t="e">
+        <v>21827.31806922135</v>
+      </c>
+      <c r="F80" s="189">
         <f t="shared" si="90"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G80" s="189" t="e">
+        <v>22224.878436611809</v>
+      </c>
+      <c r="G80" s="189">
         <f t="shared" si="90"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H80" s="189" t="e">
+        <v>22704.681171968641</v>
+      </c>
+      <c r="H80" s="189">
         <f t="shared" si="90"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I80" s="189" t="e">
+        <v>23164.898102707433</v>
+      </c>
+      <c r="I80" s="189">
         <f t="shared" si="90"/>
-        <v>#VALUE!</v>
+        <v>23637.04252909356</v>
       </c>
       <c r="K80" s="448"/>
     </row>
@@ -24171,25 +24131,25 @@
         <f t="shared" si="91"/>
         <v>4647</v>
       </c>
-      <c r="E81" s="189" t="e">
+      <c r="E81" s="189">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F81" s="189" t="e">
+        <v>4802.0229049207901</v>
+      </c>
+      <c r="F81" s="189">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G81" s="189" t="e">
+        <v>5071.275683785866</v>
+      </c>
+      <c r="G81" s="189">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H81" s="189" t="e">
+        <v>5359.9382876206082</v>
+      </c>
+      <c r="H81" s="189">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I81" s="189" t="e">
+        <v>5666.7947806794109</v>
+      </c>
+      <c r="I81" s="189">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
+        <v>5993.1529894377773</v>
       </c>
       <c r="K81" s="448"/>
     </row>
@@ -24209,25 +24169,25 @@
         <f t="shared" si="92"/>
         <v>4264</v>
       </c>
-      <c r="E82" s="189" t="e">
+      <c r="E82" s="189">
         <f t="shared" si="92"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F82" s="189" t="e">
+        <v>4361.6470393780701</v>
+      </c>
+      <c r="F82" s="189">
         <f t="shared" si="92"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G82" s="189" t="e">
+        <v>4333.2817135293235</v>
+      </c>
+      <c r="G82" s="189">
         <f t="shared" si="92"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H82" s="189" t="e">
+        <v>4349.0181750900065</v>
+      </c>
+      <c r="H82" s="189">
         <f t="shared" si="92"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I82" s="189" t="e">
+        <v>4430.4429629108799</v>
+      </c>
+      <c r="I82" s="189">
         <f t="shared" si="92"/>
-        <v>#VALUE!</v>
+        <v>4523.7068484238343</v>
       </c>
       <c r="K82" s="448"/>
     </row>
@@ -24247,25 +24207,25 @@
         <f t="shared" si="93"/>
         <v>3775</v>
       </c>
-      <c r="E83" s="189" t="e">
+      <c r="E83" s="189">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F83" s="189" t="e">
+        <v>3868.2323199498696</v>
+      </c>
+      <c r="F83" s="189">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G83" s="189" t="e">
+        <v>3937.9222622672119</v>
+      </c>
+      <c r="G83" s="189">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H83" s="189" t="e">
+        <v>4024.4012153290005</v>
+      </c>
+      <c r="H83" s="189">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I83" s="189" t="e">
+        <v>4107.7213812113305</v>
+      </c>
+      <c r="I83" s="189">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
+        <v>4193.2248107260393</v>
       </c>
       <c r="K83" s="448"/>
     </row>
@@ -24285,25 +24245,25 @@
         <f t="shared" si="94"/>
         <v>3245</v>
       </c>
-      <c r="E84" s="189" t="e">
+      <c r="E84" s="189">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F84" s="189" t="e">
+        <v>3236.3170649111844</v>
+      </c>
+      <c r="F84" s="189">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G84" s="189" t="e">
+        <v>3205.0393327359229</v>
+      </c>
+      <c r="G84" s="189">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H84" s="189" t="e">
+        <v>3276.1332193068265</v>
+      </c>
+      <c r="H84" s="189">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I84" s="189" t="e">
+        <v>3253.1752096302848</v>
+      </c>
+      <c r="I84" s="189">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
+        <v>3321.7484764778892</v>
       </c>
       <c r="K84" s="448"/>
     </row>
@@ -24399,25 +24359,25 @@
         <f t="shared" si="97"/>
         <v>13001</v>
       </c>
-      <c r="E87" s="189" t="e">
+      <c r="E87" s="189">
         <f t="shared" si="97"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F87" s="189" t="e">
+        <v>13354.807173069039</v>
+      </c>
+      <c r="F87" s="189">
         <f t="shared" si="97"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G87" s="189" t="e">
+        <v>13535.083585959212</v>
+      </c>
+      <c r="G87" s="189">
         <f t="shared" si="97"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H87" s="189" t="e">
+        <v>13924.897348213954</v>
+      </c>
+      <c r="H87" s="189">
         <f t="shared" si="97"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I87" s="189" t="e">
+        <v>14229.398073654902</v>
+      </c>
+      <c r="I87" s="189">
         <f t="shared" si="97"/>
-        <v>#VALUE!</v>
+        <v>14544.991993516547</v>
       </c>
       <c r="K87" s="448"/>
     </row>
@@ -24449,25 +24409,25 @@
         <f>D29+D52+D75</f>
         <v>82711.639514665658</v>
       </c>
-      <c r="E90" s="455" t="e">
+      <c r="E90" s="455">
         <f t="shared" ref="E90:I90" si="98">E29+E52+E75</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F90" s="455" t="e">
+        <v>82733.636396369155</v>
+      </c>
+      <c r="F90" s="455">
         <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G90" s="455" t="e">
+        <v>83093.090356396817</v>
+      </c>
+      <c r="G90" s="455">
         <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H90" s="455" t="e">
+        <v>85029.297033983748</v>
+      </c>
+      <c r="H90" s="455">
         <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I90" s="455" t="e">
+        <v>86829.389577583788</v>
+      </c>
+      <c r="I90" s="455">
         <f t="shared" si="98"/>
-        <v>#VALUE!</v>
+        <v>88896.121524738541</v>
       </c>
     </row>
   </sheetData>
@@ -24489,11 +24449,11 @@
       <c r="G2" s="156"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="C3" s="464" t="s">
+      <c r="C3" s="462" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="464"/>
-      <c r="E3" s="464"/>
+      <c r="D3" s="462"/>
+      <c r="E3" s="462"/>
       <c r="I3" s="2" t="s">
         <v>268</v>
       </c>
@@ -25014,11 +24974,11 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="C23" s="464" t="s">
+      <c r="C23" s="462" t="s">
         <v>287</v>
       </c>
-      <c r="D23" s="464"/>
-      <c r="E23" s="464"/>
+      <c r="D23" s="462"/>
+      <c r="E23" s="462"/>
       <c r="I23" s="169"/>
     </row>
     <row r="24" spans="1:12">
@@ -25180,25 +25140,25 @@
         <f>'Income statement'!F27</f>
         <v>4092</v>
       </c>
-      <c r="C31" s="158" t="e">
+      <c r="C31" s="158">
         <f>'Income statement'!H27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D31" s="158" t="e">
+        <v>4912.214417088323</v>
+      </c>
+      <c r="D31" s="158">
         <f>'Income statement'!I27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E31" s="158" t="e">
+        <v>5798.957783050444</v>
+      </c>
+      <c r="E31" s="158">
         <f>'Income statement'!J27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F31" s="158" t="e">
+        <v>5787.2821787065695</v>
+      </c>
+      <c r="F31" s="158">
         <f>'Income statement'!K27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G31" s="158" t="e">
+        <v>5883.6479534875252</v>
+      </c>
+      <c r="G31" s="158">
         <f>'Income statement'!L27</f>
-        <v>#VALUE!</v>
+        <v>5814.1306532332665</v>
       </c>
       <c r="I31" s="169"/>
     </row>
@@ -25210,25 +25170,25 @@
         <f>B31/B30</f>
         <v>17.225847190065249</v>
       </c>
-      <c r="C32" t="e">
+      <c r="C32">
         <f t="shared" ref="C32:G32" si="7">C31/C30</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D32" t="e">
+        <v>21.630182373792703</v>
+      </c>
+      <c r="D32">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E32" t="e">
+        <v>26.68273033198566</v>
+      </c>
+      <c r="E32">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F32" t="e">
+        <v>27.820796936383854</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G32" t="e">
+        <v>29.542317500941582</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="7"/>
-        <v>#VALUE!</v>
+        <v>30.485164918379123</v>
       </c>
       <c r="I32" s="169"/>
     </row>
@@ -25327,13 +25287,13 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:14" ht="21">
-      <c r="A3" s="467" t="s">
+      <c r="A3" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="467"/>
-      <c r="C3" s="467"/>
-      <c r="D3" s="467"/>
-      <c r="E3" s="467"/>
+      <c r="B3" s="465"/>
+      <c r="C3" s="465"/>
+      <c r="D3" s="465"/>
+      <c r="E3" s="465"/>
       <c r="F3" s="359"/>
       <c r="G3" s="359"/>
       <c r="H3" s="359"/>
@@ -25345,13 +25305,13 @@
       <c r="N3" s="359"/>
     </row>
     <row r="4" spans="1:14" ht="21">
-      <c r="A4" s="467" t="s">
+      <c r="A4" s="465" t="s">
         <v>296</v>
       </c>
-      <c r="B4" s="467"/>
-      <c r="C4" s="467"/>
-      <c r="D4" s="467"/>
-      <c r="E4" s="467"/>
+      <c r="B4" s="465"/>
+      <c r="C4" s="465"/>
+      <c r="D4" s="465"/>
+      <c r="E4" s="465"/>
       <c r="F4" s="359"/>
       <c r="G4" s="359"/>
       <c r="H4" s="359"/>
@@ -26045,25 +26005,25 @@
       <c r="F6">
         <v>5502</v>
       </c>
-      <c r="G6" s="158" t="e">
+      <c r="G6" s="158">
         <f>'Derived cash flow'!C57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H6" s="158" t="e">
+        <v>6308.2146834742471</v>
+      </c>
+      <c r="H6" s="158">
         <f>'Derived cash flow'!D57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I6" s="158" t="e">
+        <v>9169.929239096371</v>
+      </c>
+      <c r="I6" s="158">
         <f>'Derived cash flow'!E57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="158" t="e">
+        <v>12178.583307084713</v>
+      </c>
+      <c r="J6" s="158">
         <f>'Derived cash flow'!F57</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="158" t="e">
+        <v>15202.020062041405</v>
+      </c>
+      <c r="K6" s="158">
         <f>'Derived cash flow'!G57</f>
-        <v>#VALUE!</v>
+        <v>17608.292200726111</v>
       </c>
       <c r="N6" s="158"/>
     </row>
@@ -26086,25 +26046,25 @@
       <c r="F7">
         <v>11368</v>
       </c>
-      <c r="G7" s="158" t="e">
+      <c r="G7" s="158">
         <f>(G66*'Income statement'!H5)/365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H7" s="158" t="e">
+        <v>11207.474340738368</v>
+      </c>
+      <c r="H7" s="158">
         <f>(H66*'Income statement'!I5)/365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I7" s="158" t="e">
+        <v>11413.93753477783</v>
+      </c>
+      <c r="I7" s="158">
         <f>(I66*'Income statement'!J5)/365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="158" t="e">
+        <v>11666.902724768546</v>
+      </c>
+      <c r="J7" s="158">
         <f>(J66*'Income statement'!K5)/365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="158" t="e">
+        <v>11911.780627131486</v>
+      </c>
+      <c r="K7" s="158">
         <f>(K66*'Income statement'!L5)/365</f>
-        <v>#VALUE!</v>
+        <v>12163.11631085829</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -26126,25 +26086,25 @@
       <c r="F8">
         <v>602</v>
       </c>
-      <c r="G8" s="158" t="e">
+      <c r="G8" s="158">
         <f>'Income statement'!H12*'Balance sheet'!G67</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H8" s="158" t="e">
+        <v>593.7341018563211</v>
+      </c>
+      <c r="H8" s="158">
         <f>'Income statement'!I12*'Balance sheet'!H67</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I8" s="158" t="e">
+        <v>587.99589516992182</v>
+      </c>
+      <c r="I8" s="158">
         <f>'Income statement'!J12*'Balance sheet'!I67</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="158" t="e">
+        <v>601.03876582938517</v>
+      </c>
+      <c r="J8" s="158">
         <f>'Income statement'!K12*'Balance sheet'!J67</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="158" t="e">
+        <v>596.82689382107685</v>
+      </c>
+      <c r="K8" s="158">
         <f>'Income statement'!L12*'Balance sheet'!K67</f>
-        <v>#VALUE!</v>
+        <v>609.40733207434585</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -26166,25 +26126,25 @@
       <c r="F9">
         <v>914</v>
       </c>
-      <c r="G9" s="158" t="e">
+      <c r="G9" s="158">
         <f>G68*'Income statement'!H16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H9" s="158" t="e">
+        <v>933.01512734168466</v>
+      </c>
+      <c r="H9" s="158">
         <f>H68*'Income statement'!I16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I9" s="158" t="e">
+        <v>936.98775085959721</v>
+      </c>
+      <c r="I9" s="158">
         <f>I68*'Income statement'!J16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="158" t="e">
+        <v>958.70940354635957</v>
+      </c>
+      <c r="J9" s="158">
         <f>J68*'Income statement'!K16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K9" s="158" t="e">
+        <v>978.87628170779919</v>
+      </c>
+      <c r="K9" s="158">
         <f>K68*'Income statement'!L16</f>
-        <v>#VALUE!</v>
+        <v>1002.04387502714</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="194" customFormat="1">
@@ -26211,25 +26171,25 @@
         <f t="shared" si="0"/>
         <v>18386</v>
       </c>
-      <c r="G10" s="411" t="e">
+      <c r="G10" s="411">
         <f>SUM(G6:G9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H10" s="411" t="e">
+        <v>19042.438253410623</v>
+      </c>
+      <c r="H10" s="411">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I10" s="411" t="e">
+        <v>22108.85041990372</v>
+      </c>
+      <c r="I10" s="411">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="411" t="e">
+        <v>25405.234201229003</v>
+      </c>
+      <c r="J10" s="411">
         <f>SUM(J6:J9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="411" t="e">
+        <v>28689.503864701768</v>
+      </c>
+      <c r="K10" s="411">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>31382.859718685882</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -26686,25 +26646,25 @@
       <c r="F23">
         <v>4543</v>
       </c>
-      <c r="G23" s="158" t="e">
+      <c r="G23" s="158">
         <f>G82*'Income statement'!H5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H23" s="158" t="e">
+        <v>4193.4846770459535</v>
+      </c>
+      <c r="H23" s="158">
         <f>H82*'Income statement'!I5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I23" s="158" t="e">
+        <v>4270.7367156637283</v>
+      </c>
+      <c r="I23" s="158">
         <f>I82*'Income statement'!J5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J23" s="158" t="e">
+        <v>4365.3883397317968</v>
+      </c>
+      <c r="J23" s="158">
         <f>J82*'Income statement'!K5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K23" s="158" t="e">
+        <v>4457.0139549315982</v>
+      </c>
+      <c r="K23" s="158">
         <f>K82*'Income statement'!L5</f>
-        <v>#VALUE!</v>
+        <v>4551.0558689667805</v>
       </c>
       <c r="O23" s="158"/>
     </row>
@@ -26732,25 +26692,25 @@
         <f t="shared" si="8"/>
         <v>27599</v>
       </c>
-      <c r="G24" s="411" t="e">
+      <c r="G24" s="411">
         <f>SUM(G21:G23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H24" s="411" t="e">
+        <v>26549.484677045955</v>
+      </c>
+      <c r="H24" s="411">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I24" s="411" t="e">
+        <v>25976.736715663726</v>
+      </c>
+      <c r="I24" s="411">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J24" s="411" t="e">
+        <v>25471.388339731799</v>
+      </c>
+      <c r="J24" s="411">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K24" s="411" t="e">
+        <v>25063.013954931597</v>
+      </c>
+      <c r="K24" s="411">
         <f t="shared" si="8"/>
-        <v>#VALUE!</v>
+        <v>24757.055868966781</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -26777,25 +26737,25 @@
         <f t="shared" ref="F25:K25" si="10">F24+F19+F10</f>
         <v>87627</v>
       </c>
-      <c r="G25" s="346" t="e">
+      <c r="G25" s="346">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H25" s="346" t="e">
+        <v>91429.836359078108</v>
+      </c>
+      <c r="H25" s="346">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I25" s="346" t="e">
+        <v>96169.569268915307</v>
+      </c>
+      <c r="I25" s="346">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J25" s="346" t="e">
+        <v>101181.79446117135</v>
+      </c>
+      <c r="J25" s="346">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K25" s="346" t="e">
+        <v>106229.12169097942</v>
+      </c>
+      <c r="K25" s="346">
         <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <v>110763.07249227061</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -26878,25 +26838,25 @@
       <c r="F29">
         <v>2731</v>
       </c>
-      <c r="G29" s="158" t="e">
+      <c r="G29" s="158">
         <f>'Income statement'!H7*G88</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H29" s="158" t="e">
+        <v>2638.3995127691896</v>
+      </c>
+      <c r="H29" s="158">
         <f>'Income statement'!I7*H88</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I29" s="158" t="e">
+        <v>2620.8355537132065</v>
+      </c>
+      <c r="I29" s="158">
         <f>'Income statement'!J7*I88</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J29" s="158" t="e">
+        <v>2680.4052601854492</v>
+      </c>
+      <c r="J29" s="158">
         <f>'Income statement'!K7*J88</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K29" s="158" t="e">
+        <v>2738.289828649536</v>
+      </c>
+      <c r="K29" s="158">
         <f>'Income statement'!L7*K88</f>
-        <v>#VALUE!</v>
+        <v>2797.7206025341152</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -26918,25 +26878,25 @@
       <c r="F30">
         <v>3692</v>
       </c>
-      <c r="G30" s="158" t="e">
+      <c r="G30" s="158">
         <f>G89*'Income statement'!H16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H30" s="158" t="e">
+        <v>3723.360866955069</v>
+      </c>
+      <c r="H30" s="158">
         <f>H89*'Income statement'!I16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I30" s="158" t="e">
+        <v>3739.214319393599</v>
+      </c>
+      <c r="I30" s="158">
         <f>I89*'Income statement'!J16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J30" s="158" t="e">
+        <v>3825.8983925767579</v>
+      </c>
+      <c r="J30" s="158">
         <f>J89*'Income statement'!K16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K30" s="158" t="e">
+        <v>3906.3778647251834</v>
+      </c>
+      <c r="K30" s="158">
         <f>K89*'Income statement'!L16</f>
-        <v>#VALUE!</v>
+        <v>3998.832218163735</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -26998,25 +26958,25 @@
       <c r="F32">
         <v>4995</v>
       </c>
-      <c r="G32" s="158" t="e">
+      <c r="G32" s="158">
         <f>G91*'Income statement'!H16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H32" s="158" t="e">
+        <v>4871.0548980032445</v>
+      </c>
+      <c r="H32" s="158">
         <f>H91*'Income statement'!I16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I32" s="158" t="e">
+        <v>4891.7950410917965</v>
+      </c>
+      <c r="I32" s="158">
         <f>I91*'Income statement'!J16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J32" s="158" t="e">
+        <v>5005.1987358572205</v>
+      </c>
+      <c r="J32" s="158">
         <f>J91*'Income statement'!K16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K32" s="158" t="e">
+        <v>5110.4853145706866</v>
+      </c>
+      <c r="K32" s="158">
         <f>K91*'Income statement'!L16</f>
-        <v>#VALUE!</v>
+        <v>5231.4379289561066</v>
       </c>
     </row>
     <row r="33" spans="1:60" s="194" customFormat="1">
@@ -27043,25 +27003,25 @@
         <f>SUM(F28:F32)</f>
         <v>15411</v>
       </c>
-      <c r="G33" s="411" t="e">
+      <c r="G33" s="411">
         <f>SUM(G28:G32)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H33" s="411" t="e">
+        <v>14966.765277727503</v>
+      </c>
+      <c r="H33" s="411">
         <f t="shared" ref="H33:K33" si="12">SUM(H28:H32)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I33" s="411" t="e">
+        <v>14993.294914198601</v>
+      </c>
+      <c r="I33" s="411">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J33" s="411" t="e">
+        <v>14238.952388619427</v>
+      </c>
+      <c r="J33" s="411">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K33" s="411" t="e">
+        <v>14990.603007945407</v>
+      </c>
+      <c r="K33" s="411">
         <f t="shared" si="12"/>
-        <v>#VALUE!</v>
+        <v>15870.440749653957</v>
       </c>
       <c r="O33" s="161"/>
       <c r="P33" s="161"/>
@@ -27218,25 +27178,25 @@
       <c r="F38">
         <v>4033</v>
       </c>
-      <c r="G38" s="158" t="e">
+      <c r="G38" s="158">
         <f>G97*'Income statement'!H16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H38" s="158" t="e">
+        <v>4340.7874924623311</v>
+      </c>
+      <c r="H38" s="158">
         <f>H97*'Income statement'!I16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I38" s="158" t="e">
+        <v>4666.78357308264</v>
+      </c>
+      <c r="I38" s="158">
         <f>I97*'Income statement'!J16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J38" s="158" t="e">
+        <v>5089.6135988073138</v>
+      </c>
+      <c r="J38" s="158">
         <f>J97*'Income statement'!K16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="158" t="e">
+        <v>5517.9371729335289</v>
+      </c>
+      <c r="K38" s="158">
         <f>K97*'Income statement'!L16</f>
-        <v>#VALUE!</v>
+        <v>5977.3979260366077</v>
       </c>
       <c r="O38" s="158"/>
     </row>
@@ -27299,25 +27259,25 @@
       <c r="F40">
         <v>783</v>
       </c>
-      <c r="G40" s="158" t="e">
+      <c r="G40" s="158">
         <f>G99*'Income statement'!H5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H40" s="158" t="e">
+        <v>775.90567847322097</v>
+      </c>
+      <c r="H40" s="158">
         <f>H99*'Income statement'!I5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I40" s="158" t="e">
+        <v>790.19935069414532</v>
+      </c>
+      <c r="I40" s="158">
         <f>I99*'Income statement'!J5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J40" s="158" t="e">
+        <v>807.71240683886481</v>
+      </c>
+      <c r="J40" s="158">
         <f>J99*'Income statement'!K5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K40" s="158" t="e">
+        <v>824.66557123607186</v>
+      </c>
+      <c r="K40" s="158">
         <f>K99*'Income statement'!L5</f>
-        <v>#VALUE!</v>
+        <v>842.06581488398444</v>
       </c>
     </row>
     <row r="41" spans="1:60" s="194" customFormat="1">
@@ -27344,25 +27304,25 @@
         <f t="shared" si="15"/>
         <v>24991</v>
       </c>
-      <c r="G41" s="411" t="e">
+      <c r="G41" s="411">
         <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H41" s="411" t="e">
+        <v>25323.037607127368</v>
+      </c>
+      <c r="H41" s="411">
         <f t="shared" ref="H41:K41" si="16">SUM(H36:H40)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I41" s="411" t="e">
+        <v>25369.633164228224</v>
+      </c>
+      <c r="I41" s="411">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J41" s="411" t="e">
+        <v>25591.814113950171</v>
+      </c>
+      <c r="J41" s="411">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K41" s="411" t="e">
+        <v>25868.839697803829</v>
+      </c>
+      <c r="K41" s="411">
         <f t="shared" si="16"/>
-        <v>#VALUE!</v>
+        <v>26284.673535857488</v>
       </c>
     </row>
     <row r="42" spans="1:60">
@@ -27469,25 +27429,25 @@
       <c r="F45">
         <v>41402</v>
       </c>
-      <c r="G45" s="158" t="e">
+      <c r="G45" s="158">
         <f>G161</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H45" s="158" t="e">
+        <v>44985.783474223237</v>
+      </c>
+      <c r="H45" s="158">
         <f t="shared" ref="H45:J45" si="18">H161</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I45" s="158" t="e">
+        <v>49426.141190488474</v>
+      </c>
+      <c r="I45" s="158">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J45" s="158" t="e">
+        <v>53820.277958601757</v>
+      </c>
+      <c r="J45" s="158">
         <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K45" s="158" t="e">
+        <v>58271.678985230188</v>
+      </c>
+      <c r="K45" s="158">
         <f>K161</f>
-        <v>#VALUE!</v>
+        <v>62609.708206759169</v>
       </c>
       <c r="M45" s="158"/>
       <c r="O45" s="158"/>
@@ -27592,25 +27552,25 @@
         <f>SUM(F43:F47)</f>
         <v>28074</v>
       </c>
-      <c r="G48" s="411" t="e">
+      <c r="G48" s="411">
         <f>SUM(G43:G47)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H48" s="411" t="e">
+        <v>29360.033474223237</v>
+      </c>
+      <c r="H48" s="411">
         <f t="shared" ref="H48:K48" si="19">SUM(H43:H47)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I48" s="411" t="e">
+        <v>31502.641190488474</v>
+      </c>
+      <c r="I48" s="411">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J48" s="411" t="e">
+        <v>33599.027958601757</v>
+      </c>
+      <c r="J48" s="411">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K48" s="411" t="e">
+        <v>35752.678985230188</v>
+      </c>
+      <c r="K48" s="411">
         <f t="shared" si="19"/>
-        <v>#VALUE!</v>
+        <v>37792.958206759169</v>
       </c>
       <c r="N48" s="158"/>
       <c r="AY48"/>
@@ -27648,25 +27608,25 @@
         <f>F48+F41+F33+F34</f>
         <v>87627</v>
       </c>
-      <c r="G49" s="346" t="e">
+      <c r="G49" s="346">
         <f>G48+G41+G33+G34</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H49" s="346" t="e">
+        <v>91429.836359078108</v>
+      </c>
+      <c r="H49" s="346">
         <f t="shared" ref="H49:K49" si="21">H48+H41+H33+H34</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I49" s="346" t="e">
+        <v>96169.569268915293</v>
+      </c>
+      <c r="I49" s="346">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J49" s="346" t="e">
+        <v>101181.79446117135</v>
+      </c>
+      <c r="J49" s="346">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K49" s="346" t="e">
+        <v>106229.12169097943</v>
+      </c>
+      <c r="K49" s="346">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>110763.07249227061</v>
       </c>
       <c r="N49" s="158"/>
     </row>
@@ -27674,25 +27634,25 @@
       <c r="A51" t="s">
         <v>359</v>
       </c>
-      <c r="G51" s="158" t="e">
+      <c r="G51" s="158">
         <f>G49-G25</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H51" s="158" t="e">
+        <v>0</v>
+      </c>
+      <c r="H51" s="158">
         <f t="shared" ref="H51:K51" si="22">H49-H25</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I51" s="158" t="e">
+        <v>0</v>
+      </c>
+      <c r="I51" s="158">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J51" s="158" t="e">
+        <v>0</v>
+      </c>
+      <c r="J51" s="158">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K51" s="158" t="e">
+        <v>0</v>
+      </c>
+      <c r="K51" s="158">
         <f t="shared" si="22"/>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:60">
@@ -28613,25 +28573,25 @@
         <f t="shared" si="37"/>
         <v>19151</v>
       </c>
-      <c r="G93" s="158" t="e">
+      <c r="G93" s="158">
         <f>SUM(G7:G9,G19,G21:G23)*G175</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H93" s="158" t="e">
+        <v>23834.05406916908</v>
+      </c>
+      <c r="H93" s="158">
         <f>SUM(H7:H9,H19,H21:H23)*H175</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I93" s="158" t="e">
+        <v>25229.895608647486</v>
+      </c>
+      <c r="I93" s="158">
         <f>SUM(I7:I9,I19,I21:I23)*I175</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J93" s="158" t="e">
+        <v>26700.963346225992</v>
+      </c>
+      <c r="J93" s="158">
         <f>SUM(J7:J9,J19,J21:J23)*J175</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K93" s="158" t="e">
+        <v>27308.1304886814</v>
+      </c>
+      <c r="K93" s="158">
         <f>SUM(K7:K9,K19,K21:K23)*K175</f>
-        <v>#VALUE!</v>
+        <v>27946.434087463353</v>
       </c>
       <c r="N93" s="163"/>
     </row>
@@ -29053,13 +29013,13 @@
       <c r="H118" t="s">
         <v>389</v>
       </c>
-      <c r="M118" s="469" t="s">
+      <c r="M118" s="467" t="s">
         <v>269</v>
       </c>
-      <c r="N118" s="468" t="s">
+      <c r="N118" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="O118" s="466"/>
+      <c r="O118" s="464"/>
     </row>
     <row r="119" spans="1:19">
       <c r="A119" s="355" t="s">
@@ -29088,9 +29048,9 @@
         <f>SUM(G117:G118)</f>
         <v>36929</v>
       </c>
-      <c r="M119" s="469"/>
-      <c r="N119" s="468"/>
-      <c r="O119" s="466"/>
+      <c r="M119" s="467"/>
+      <c r="N119" s="466"/>
+      <c r="O119" s="464"/>
     </row>
     <row r="120" spans="1:19">
       <c r="A120" s="184"/>
@@ -29993,21 +29953,21 @@
       <c r="G155" s="173">
         <v>41402</v>
       </c>
-      <c r="H155" s="173" t="e">
+      <c r="H155" s="173">
         <f t="shared" ref="H155:J155" si="52">G161</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I155" s="173" t="e">
+        <v>44985.783474223237</v>
+      </c>
+      <c r="I155" s="173">
         <f t="shared" si="52"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J155" s="173" t="e">
+        <v>49426.141190488474</v>
+      </c>
+      <c r="J155" s="173">
         <f t="shared" si="52"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K155" s="182" t="e">
+        <v>53820.277958601757</v>
+      </c>
+      <c r="K155" s="182">
         <f>J161</f>
-        <v>#VALUE!</v>
+        <v>58271.678985230188</v>
       </c>
       <c r="L155" s="173"/>
       <c r="M155" s="172"/>
@@ -30020,25 +29980,25 @@
       <c r="F156" s="173">
         <v>4092</v>
       </c>
-      <c r="G156" s="173" t="e">
+      <c r="G156" s="173">
         <f>'Income statement'!H27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H156" s="173" t="e">
+        <v>4912.214417088323</v>
+      </c>
+      <c r="H156" s="173">
         <f>'Income statement'!I27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I156" s="173" t="e">
+        <v>5798.957783050444</v>
+      </c>
+      <c r="I156" s="173">
         <f>'Income statement'!J27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J156" s="173" t="e">
+        <v>5787.2821787065695</v>
+      </c>
+      <c r="J156" s="173">
         <f>'Income statement'!K27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K156" s="182" t="e">
+        <v>5883.6479534875252</v>
+      </c>
+      <c r="K156" s="182">
         <f>'Income statement'!L27</f>
-        <v>#VALUE!</v>
+        <v>5814.1306532332665</v>
       </c>
       <c r="L156" s="173"/>
       <c r="M156" s="172"/>
@@ -30181,25 +30141,25 @@
       <c r="F161" s="350">
         <v>44894</v>
       </c>
-      <c r="G161" s="350" t="e">
+      <c r="G161" s="350">
         <f>G155+G156-G158</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H161" s="350" t="e">
+        <v>44985.783474223237</v>
+      </c>
+      <c r="H161" s="350">
         <f t="shared" ref="H161:K161" si="56">H155+H156-H158</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I161" s="350" t="e">
+        <v>49426.141190488474</v>
+      </c>
+      <c r="I161" s="350">
         <f t="shared" si="56"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J161" s="350" t="e">
+        <v>53820.277958601757</v>
+      </c>
+      <c r="J161" s="350">
         <f t="shared" si="56"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K161" s="351" t="e">
+        <v>58271.678985230188</v>
+      </c>
+      <c r="K161" s="351">
         <f t="shared" si="56"/>
-        <v>#VALUE!</v>
+        <v>62609.708206759169</v>
       </c>
       <c r="L161" s="173"/>
       <c r="M161" s="172"/>
@@ -30207,9 +30167,9 @@
     </row>
     <row r="162" spans="1:19">
       <c r="A162" s="163"/>
-      <c r="G162" s="170" t="e">
+      <c r="G162" s="170">
         <f>G161-F161</f>
-        <v>#VALUE!</v>
+        <v>91.783474223237135</v>
       </c>
       <c r="K162" s="178"/>
       <c r="L162" s="173"/>
